--- a/data/weeks/AKP_PS_16_09_2026-24_09_2026.xlsx
+++ b/data/weeks/AKP_PS_16_09_2026-24_09_2026.xlsx
@@ -5,18 +5,19 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026 Data\AKP Smart Policing Data\WEB UPLOADS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kolak\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D466033E-F1E0-41C1-9EB6-4997F3A06501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{42EBAC1B-0F0A-4835-98EA-4A7AB88DB5C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{97DF618B-34EB-498F-A854-1F66342AE975}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{97DF618B-34EB-498F-A854-1F66342AE975}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Sheet1!$1:$2</definedName>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="60">
   <si>
     <t>District</t>
   </si>
@@ -91,15 +92,6 @@
   </si>
   <si>
     <t xml:space="preserve">APOLIS </t>
-  </si>
-  <si>
-    <t>Drone Flying</t>
-  </si>
-  <si>
-    <t>Dial112 Tabs</t>
-  </si>
-  <si>
-    <t>Dial112 Resp</t>
   </si>
   <si>
     <t>CCTV360 Usage</t>
@@ -218,12 +210,24 @@
   <si>
     <t>Yelamanchili Traffic</t>
   </si>
+  <si>
+    <t>NATGRID</t>
+  </si>
+  <si>
+    <t>APOLIS Util</t>
+  </si>
+  <si>
+    <t>APOLIS Files</t>
+  </si>
+  <si>
+    <t>eDAR</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -273,8 +277,14 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF2C3FAE"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -311,8 +321,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7F9FD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -335,11 +351,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFE4E9F1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -369,6 +394,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -391,7 +428,6 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="1_MEDLEAPR_PME"/>
@@ -14758,594 +14794,6 @@
           <cell r="B2" t="str">
             <v>PS</v>
           </cell>
-          <cell r="C2" t="str">
-            <v>Is Drone Available</v>
-          </cell>
-          <cell r="D2" t="str">
-            <v>Hours</v>
-          </cell>
-          <cell r="E2" t="str">
-            <v>Min</v>
-          </cell>
-          <cell r="F2" t="str">
-            <v>Sec</v>
-          </cell>
-          <cell r="G2" t="str">
-            <v>Total Seconds</v>
-          </cell>
-          <cell r="H2" t="str">
-            <v>Flying  Value
-(80%)</v>
-          </cell>
-          <cell r="I2" t="str">
-            <v>Enforce
-ment
-( 20%)</v>
-          </cell>
-          <cell r="J2" t="str">
-            <v>Raw Value</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>A.Koduru</v>
-          </cell>
-          <cell r="C3" t="str">
-            <v>NO</v>
-          </cell>
-          <cell r="G3">
-            <v>-1</v>
-          </cell>
-          <cell r="H3">
-            <v>20</v>
-          </cell>
-          <cell r="J3">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="B4" t="str">
-            <v>Anakapalli Rural</v>
-          </cell>
-          <cell r="C4" t="str">
-            <v>YES</v>
-          </cell>
-          <cell r="G4">
-            <v>-1</v>
-          </cell>
-          <cell r="H4">
-            <v>20</v>
-          </cell>
-          <cell r="J4">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="B5" t="str">
-            <v>Anakapalli Town</v>
-          </cell>
-          <cell r="C5" t="str">
-            <v>YES</v>
-          </cell>
-          <cell r="G5">
-            <v>-1</v>
-          </cell>
-          <cell r="H5">
-            <v>20</v>
-          </cell>
-          <cell r="J5">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="B6" t="str">
-            <v>Anakapalli Traffic</v>
-          </cell>
-          <cell r="C6" t="str">
-            <v>YES</v>
-          </cell>
-          <cell r="G6">
-            <v>-1</v>
-          </cell>
-          <cell r="H6">
-            <v>20</v>
-          </cell>
-          <cell r="J6">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7" t="str">
-            <v>Atchutapuram</v>
-          </cell>
-          <cell r="C7" t="str">
-            <v>YES</v>
-          </cell>
-          <cell r="G7">
-            <v>-1</v>
-          </cell>
-          <cell r="H7">
-            <v>20</v>
-          </cell>
-          <cell r="J7">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="B8" t="str">
-            <v>Butchiyyapeta</v>
-          </cell>
-          <cell r="C8" t="str">
-            <v>NO</v>
-          </cell>
-          <cell r="G8">
-            <v>-1</v>
-          </cell>
-          <cell r="H8">
-            <v>20</v>
-          </cell>
-          <cell r="J8">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="B9" t="str">
-            <v>Cheedikada</v>
-          </cell>
-          <cell r="C9" t="str">
-            <v>NO</v>
-          </cell>
-          <cell r="G9">
-            <v>-1</v>
-          </cell>
-          <cell r="H9">
-            <v>20</v>
-          </cell>
-          <cell r="J9">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="B10" t="str">
-            <v>Chodavaram</v>
-          </cell>
-          <cell r="C10" t="str">
-            <v>YES</v>
-          </cell>
-          <cell r="G10">
-            <v>-1</v>
-          </cell>
-          <cell r="H10">
-            <v>20</v>
-          </cell>
-          <cell r="J10">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="B11" t="str">
-            <v>Devarapalli</v>
-          </cell>
-          <cell r="C11" t="str">
-            <v>NO</v>
-          </cell>
-          <cell r="G11">
-            <v>-1</v>
-          </cell>
-          <cell r="H11">
-            <v>20</v>
-          </cell>
-          <cell r="J11">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="B12" t="str">
-            <v>Golugonda</v>
-          </cell>
-          <cell r="C12" t="str">
-            <v>NO</v>
-          </cell>
-          <cell r="G12">
-            <v>-1</v>
-          </cell>
-          <cell r="H12">
-            <v>20</v>
-          </cell>
-          <cell r="J12">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="B13" t="str">
-            <v>K.D.Peta</v>
-          </cell>
-          <cell r="C13" t="str">
-            <v>YES</v>
-          </cell>
-          <cell r="G13">
-            <v>-1</v>
-          </cell>
-          <cell r="H13">
-            <v>20</v>
-          </cell>
-          <cell r="J13">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="B14" t="str">
-            <v>K.Kotapadu</v>
-          </cell>
-          <cell r="C14" t="str">
-            <v>YES</v>
-          </cell>
-          <cell r="G14">
-            <v>-1</v>
-          </cell>
-          <cell r="H14">
-            <v>20</v>
-          </cell>
-          <cell r="J14">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="B15" t="str">
-            <v>Kasimkota</v>
-          </cell>
-          <cell r="C15" t="str">
-            <v>YES</v>
-          </cell>
-          <cell r="G15">
-            <v>-1</v>
-          </cell>
-          <cell r="H15">
-            <v>20</v>
-          </cell>
-          <cell r="J15">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="B16" t="str">
-            <v>Kotavurtla</v>
-          </cell>
-          <cell r="C16" t="str">
-            <v>NO</v>
-          </cell>
-          <cell r="G16">
-            <v>-1</v>
-          </cell>
-          <cell r="H16">
-            <v>20</v>
-          </cell>
-          <cell r="J16">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="B17" t="str">
-            <v>Kothakota</v>
-          </cell>
-          <cell r="C17" t="str">
-            <v>YES</v>
-          </cell>
-          <cell r="G17">
-            <v>-1</v>
-          </cell>
-          <cell r="H17">
-            <v>20</v>
-          </cell>
-          <cell r="J17">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="B18" t="str">
-            <v>Mahila UPS, Anakapalli</v>
-          </cell>
-          <cell r="C18" t="str">
-            <v>NO</v>
-          </cell>
-          <cell r="G18">
-            <v>-1</v>
-          </cell>
-          <cell r="H18">
-            <v>20</v>
-          </cell>
-          <cell r="J18">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="B19" t="str">
-            <v>Makavarapalem</v>
-          </cell>
-          <cell r="C19" t="str">
-            <v>YES</v>
-          </cell>
-          <cell r="G19">
-            <v>-1</v>
-          </cell>
-          <cell r="H19">
-            <v>20</v>
-          </cell>
-          <cell r="J19">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="B20" t="str">
-            <v>Munagapaka</v>
-          </cell>
-          <cell r="C20" t="str">
-            <v>NO</v>
-          </cell>
-          <cell r="G20">
-            <v>-1</v>
-          </cell>
-          <cell r="H20">
-            <v>20</v>
-          </cell>
-          <cell r="J20">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="B21" t="str">
-            <v>Nakkapalli</v>
-          </cell>
-          <cell r="C21" t="str">
-            <v>YES</v>
-          </cell>
-          <cell r="G21">
-            <v>-1</v>
-          </cell>
-          <cell r="H21">
-            <v>20</v>
-          </cell>
-          <cell r="J21">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="B22" t="str">
-            <v>Narsipatnam Rural</v>
-          </cell>
-          <cell r="C22" t="str">
-            <v>YES</v>
-          </cell>
-          <cell r="G22">
-            <v>-1</v>
-          </cell>
-          <cell r="H22">
-            <v>20</v>
-          </cell>
-          <cell r="J22">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="B23" t="str">
-            <v>Narsipatnam Town</v>
-          </cell>
-          <cell r="C23" t="str">
-            <v>YES</v>
-          </cell>
-          <cell r="G23">
-            <v>-1</v>
-          </cell>
-          <cell r="H23">
-            <v>20</v>
-          </cell>
-          <cell r="J23">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="B24" t="str">
-            <v>Nathavaram</v>
-          </cell>
-          <cell r="C24" t="str">
-            <v>NO</v>
-          </cell>
-          <cell r="G24">
-            <v>-1</v>
-          </cell>
-          <cell r="H24">
-            <v>20</v>
-          </cell>
-          <cell r="J24">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="B25" t="str">
-            <v>Parawada</v>
-          </cell>
-          <cell r="C25" t="str">
-            <v>YES</v>
-          </cell>
-          <cell r="G25">
-            <v>-1</v>
-          </cell>
-          <cell r="H25">
-            <v>20</v>
-          </cell>
-          <cell r="J25">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="B26" t="str">
-            <v>Payakaraopeta</v>
-          </cell>
-          <cell r="C26" t="str">
-            <v>YES</v>
-          </cell>
-          <cell r="G26">
-            <v>-1</v>
-          </cell>
-          <cell r="H26">
-            <v>20</v>
-          </cell>
-          <cell r="J26">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="B27" t="str">
-            <v>Rambilli</v>
-          </cell>
-          <cell r="C27" t="str">
-            <v>YES</v>
-          </cell>
-          <cell r="G27">
-            <v>-1</v>
-          </cell>
-          <cell r="H27">
-            <v>20</v>
-          </cell>
-          <cell r="J27">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="B28" t="str">
-            <v>Ravikamatham</v>
-          </cell>
-          <cell r="C28" t="str">
-            <v>NO</v>
-          </cell>
-          <cell r="G28">
-            <v>-1</v>
-          </cell>
-          <cell r="H28">
-            <v>20</v>
-          </cell>
-          <cell r="J28">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="B29" t="str">
-            <v>Rolugunta</v>
-          </cell>
-          <cell r="C29" t="str">
-            <v>NO</v>
-          </cell>
-          <cell r="G29">
-            <v>-1</v>
-          </cell>
-          <cell r="H29">
-            <v>20</v>
-          </cell>
-          <cell r="J29">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="B30" t="str">
-            <v>S.Rayavaram</v>
-          </cell>
-          <cell r="C30" t="str">
-            <v>YES</v>
-          </cell>
-          <cell r="G30">
-            <v>-1</v>
-          </cell>
-          <cell r="H30">
-            <v>20</v>
-          </cell>
-          <cell r="J30">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="B31" t="str">
-            <v>Sabbavaram</v>
-          </cell>
-          <cell r="C31" t="str">
-            <v>NO</v>
-          </cell>
-          <cell r="G31">
-            <v>-1</v>
-          </cell>
-          <cell r="H31">
-            <v>20</v>
-          </cell>
-          <cell r="J31">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="B32" t="str">
-            <v>V.Madugula</v>
-          </cell>
-          <cell r="C32" t="str">
-            <v>NO</v>
-          </cell>
-          <cell r="G32">
-            <v>-1</v>
-          </cell>
-          <cell r="H32">
-            <v>20</v>
-          </cell>
-          <cell r="J32">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="B33" t="str">
-            <v>Yelamanchili Rural</v>
-          </cell>
-          <cell r="C33" t="str">
-            <v>NO</v>
-          </cell>
-          <cell r="G33">
-            <v>-1</v>
-          </cell>
-          <cell r="H33">
-            <v>20</v>
-          </cell>
-          <cell r="J33">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="B34" t="str">
-            <v>Yelamanchili Town</v>
-          </cell>
-          <cell r="C34" t="str">
-            <v>YES</v>
-          </cell>
-          <cell r="G34">
-            <v>-1</v>
-          </cell>
-          <cell r="H34">
-            <v>20</v>
-          </cell>
-          <cell r="J34">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="B35" t="str">
-            <v>Yelamanchili Traffic</v>
-          </cell>
-          <cell r="C35" t="str">
-            <v>YES</v>
-          </cell>
-          <cell r="G35">
-            <v>-1</v>
-          </cell>
-          <cell r="H35">
-            <v>20</v>
-          </cell>
-          <cell r="J35">
-            <v>0</v>
-          </cell>
         </row>
       </sheetData>
       <sheetData sheetId="17">
@@ -15353,915 +14801,12 @@
           <cell r="B2" t="str">
             <v>PS</v>
           </cell>
-          <cell r="C2" t="str">
-            <v>Total Tabs
- Config</v>
-          </cell>
-          <cell r="D2" t="str">
-            <v>ERU Connected Live</v>
-          </cell>
-          <cell r="E2" t="str">
-            <v>Dis-connected Tabs</v>
-          </cell>
-          <cell r="F2" t="str">
-            <v>% of Disconnected Tabs</v>
-          </cell>
-          <cell r="G2" t="str">
-            <v>Raw Value</v>
-          </cell>
-          <cell r="H2" t="str">
-            <v>Marks</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>A.Koduru</v>
-          </cell>
-          <cell r="F3">
-            <v>0</v>
-          </cell>
-          <cell r="G3">
-            <v>0</v>
-          </cell>
-          <cell r="H3">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="B4" t="str">
-            <v>Anakapalli Rural</v>
-          </cell>
-          <cell r="F4">
-            <v>0</v>
-          </cell>
-          <cell r="G4">
-            <v>0</v>
-          </cell>
-          <cell r="H4">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="B5" t="str">
-            <v>Anakapalli Town</v>
-          </cell>
-          <cell r="F5">
-            <v>0</v>
-          </cell>
-          <cell r="G5">
-            <v>0</v>
-          </cell>
-          <cell r="H5">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="B6" t="str">
-            <v>Anakapalli Traffic</v>
-          </cell>
-          <cell r="F6">
-            <v>0</v>
-          </cell>
-          <cell r="G6">
-            <v>0</v>
-          </cell>
-          <cell r="H6">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7" t="str">
-            <v>Atchutapuram</v>
-          </cell>
-          <cell r="F7">
-            <v>0</v>
-          </cell>
-          <cell r="G7">
-            <v>0</v>
-          </cell>
-          <cell r="H7">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="B8" t="str">
-            <v>Butchiyyapeta</v>
-          </cell>
-          <cell r="F8">
-            <v>0</v>
-          </cell>
-          <cell r="G8">
-            <v>0</v>
-          </cell>
-          <cell r="H8">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="B9" t="str">
-            <v>Cheedikada</v>
-          </cell>
-          <cell r="F9">
-            <v>0</v>
-          </cell>
-          <cell r="G9">
-            <v>0</v>
-          </cell>
-          <cell r="H9">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="B10" t="str">
-            <v>Chodavaram</v>
-          </cell>
-          <cell r="F10">
-            <v>0</v>
-          </cell>
-          <cell r="G10">
-            <v>0</v>
-          </cell>
-          <cell r="H10">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="B11" t="str">
-            <v>Devarapalli</v>
-          </cell>
-          <cell r="F11">
-            <v>0</v>
-          </cell>
-          <cell r="G11">
-            <v>0</v>
-          </cell>
-          <cell r="H11">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="B12" t="str">
-            <v>Golugonda</v>
-          </cell>
-          <cell r="F12">
-            <v>0</v>
-          </cell>
-          <cell r="G12">
-            <v>0</v>
-          </cell>
-          <cell r="H12">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="B13" t="str">
-            <v>K.D.Peta</v>
-          </cell>
-          <cell r="F13">
-            <v>0</v>
-          </cell>
-          <cell r="G13">
-            <v>0</v>
-          </cell>
-          <cell r="H13">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="B14" t="str">
-            <v>K.Kotapadu</v>
-          </cell>
-          <cell r="F14">
-            <v>0</v>
-          </cell>
-          <cell r="G14">
-            <v>0</v>
-          </cell>
-          <cell r="H14">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="B15" t="str">
-            <v>Kasimkota</v>
-          </cell>
-          <cell r="F15">
-            <v>0</v>
-          </cell>
-          <cell r="G15">
-            <v>0</v>
-          </cell>
-          <cell r="H15">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="B16" t="str">
-            <v>Kotavurtla</v>
-          </cell>
-          <cell r="F16">
-            <v>0</v>
-          </cell>
-          <cell r="G16">
-            <v>0</v>
-          </cell>
-          <cell r="H16">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="B17" t="str">
-            <v>Kothakota</v>
-          </cell>
-          <cell r="F17">
-            <v>0</v>
-          </cell>
-          <cell r="G17">
-            <v>0</v>
-          </cell>
-          <cell r="H17">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="B18" t="str">
-            <v>Mahila UPS, Anakapalli</v>
-          </cell>
-          <cell r="F18">
-            <v>0</v>
-          </cell>
-          <cell r="G18">
-            <v>0</v>
-          </cell>
-          <cell r="H18">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="B19" t="str">
-            <v>Makavarapalem</v>
-          </cell>
-          <cell r="F19">
-            <v>0</v>
-          </cell>
-          <cell r="G19">
-            <v>0</v>
-          </cell>
-          <cell r="H19">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="B20" t="str">
-            <v>Munagapaka</v>
-          </cell>
-          <cell r="F20">
-            <v>0</v>
-          </cell>
-          <cell r="G20">
-            <v>0</v>
-          </cell>
-          <cell r="H20">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="B21" t="str">
-            <v>Nakkapalli</v>
-          </cell>
-          <cell r="F21">
-            <v>0</v>
-          </cell>
-          <cell r="G21">
-            <v>0</v>
-          </cell>
-          <cell r="H21">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="B22" t="str">
-            <v>Narsipatnam Rural</v>
-          </cell>
-          <cell r="F22">
-            <v>0</v>
-          </cell>
-          <cell r="G22">
-            <v>0</v>
-          </cell>
-          <cell r="H22">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="B23" t="str">
-            <v>Narsipatnam Town</v>
-          </cell>
-          <cell r="F23">
-            <v>0</v>
-          </cell>
-          <cell r="G23">
-            <v>0</v>
-          </cell>
-          <cell r="H23">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="B24" t="str">
-            <v>Nathavaram</v>
-          </cell>
-          <cell r="F24">
-            <v>0</v>
-          </cell>
-          <cell r="G24">
-            <v>0</v>
-          </cell>
-          <cell r="H24">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="B25" t="str">
-            <v>Parawada</v>
-          </cell>
-          <cell r="F25">
-            <v>0</v>
-          </cell>
-          <cell r="G25">
-            <v>0</v>
-          </cell>
-          <cell r="H25">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="B26" t="str">
-            <v>Payakaraopeta</v>
-          </cell>
-          <cell r="F26">
-            <v>0</v>
-          </cell>
-          <cell r="G26">
-            <v>0</v>
-          </cell>
-          <cell r="H26">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="B27" t="str">
-            <v>Rambilli</v>
-          </cell>
-          <cell r="F27">
-            <v>0</v>
-          </cell>
-          <cell r="G27">
-            <v>0</v>
-          </cell>
-          <cell r="H27">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="B28" t="str">
-            <v>Ravikamatham</v>
-          </cell>
-          <cell r="F28">
-            <v>0</v>
-          </cell>
-          <cell r="G28">
-            <v>0</v>
-          </cell>
-          <cell r="H28">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="B29" t="str">
-            <v>Rolugunta</v>
-          </cell>
-          <cell r="F29">
-            <v>0</v>
-          </cell>
-          <cell r="G29">
-            <v>0</v>
-          </cell>
-          <cell r="H29">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="B30" t="str">
-            <v>S.Rayavaram</v>
-          </cell>
-          <cell r="F30">
-            <v>0</v>
-          </cell>
-          <cell r="G30">
-            <v>0</v>
-          </cell>
-          <cell r="H30">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="B31" t="str">
-            <v>Sabbavaram</v>
-          </cell>
-          <cell r="F31">
-            <v>0</v>
-          </cell>
-          <cell r="G31">
-            <v>0</v>
-          </cell>
-          <cell r="H31">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="B32" t="str">
-            <v>V.Madugula</v>
-          </cell>
-          <cell r="F32">
-            <v>0</v>
-          </cell>
-          <cell r="G32">
-            <v>0</v>
-          </cell>
-          <cell r="H32">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="B33" t="str">
-            <v>Yelamanchili Rural</v>
-          </cell>
-          <cell r="F33">
-            <v>0</v>
-          </cell>
-          <cell r="G33">
-            <v>0</v>
-          </cell>
-          <cell r="H33">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="B34" t="str">
-            <v>Yelamanchili Town</v>
-          </cell>
-          <cell r="F34">
-            <v>0</v>
-          </cell>
-          <cell r="G34">
-            <v>0</v>
-          </cell>
-          <cell r="H34">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="B35" t="str">
-            <v>Yelamanchili Traffic</v>
-          </cell>
-          <cell r="F35">
-            <v>0</v>
-          </cell>
-          <cell r="G35">
-            <v>0</v>
-          </cell>
-          <cell r="H35">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="C36">
-            <v>0</v>
-          </cell>
-          <cell r="D36">
-            <v>0</v>
-          </cell>
-          <cell r="E36">
-            <v>0</v>
-          </cell>
-          <cell r="F36">
-            <v>0</v>
-          </cell>
-          <cell r="G36">
-            <v>0</v>
-          </cell>
-          <cell r="H36">
-            <v>0</v>
-          </cell>
         </row>
       </sheetData>
       <sheetData sheetId="18">
         <row r="2">
           <cell r="B2" t="str">
             <v>PS</v>
-          </cell>
-          <cell r="C2" t="str">
-            <v>Total calls Assigned to PS</v>
-          </cell>
-          <cell r="D2" t="str">
-            <v>No. of Calls Assigned to Tabs by PS</v>
-          </cell>
-          <cell r="E2" t="str">
-            <v>No. of Calls not Assigned to Tabs by PS</v>
-          </cell>
-          <cell r="F2" t="str">
-            <v xml:space="preserve"> Average Response Time
-(HH:MM:SS)</v>
-          </cell>
-          <cell r="G2" t="str">
-            <v>Raw Value</v>
-          </cell>
-          <cell r="H2" t="str">
-            <v>Marks</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>A.Koduru</v>
-          </cell>
-          <cell r="G3">
-            <v>0</v>
-          </cell>
-          <cell r="H3">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="B4" t="str">
-            <v>Anakapalli Rural</v>
-          </cell>
-          <cell r="G4">
-            <v>0</v>
-          </cell>
-          <cell r="H4">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="B5" t="str">
-            <v>Anakapalli Town</v>
-          </cell>
-          <cell r="G5">
-            <v>0</v>
-          </cell>
-          <cell r="H5">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="B6" t="str">
-            <v>Anakapalli Traffic</v>
-          </cell>
-          <cell r="G6">
-            <v>0</v>
-          </cell>
-          <cell r="H6">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7" t="str">
-            <v>Atchutapuram</v>
-          </cell>
-          <cell r="G7">
-            <v>0</v>
-          </cell>
-          <cell r="H7">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="B8" t="str">
-            <v>Butchiyyapeta</v>
-          </cell>
-          <cell r="G8">
-            <v>0</v>
-          </cell>
-          <cell r="H8">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="B9" t="str">
-            <v>Cheedikada</v>
-          </cell>
-          <cell r="G9">
-            <v>0</v>
-          </cell>
-          <cell r="H9">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="B10" t="str">
-            <v>Chodavaram</v>
-          </cell>
-          <cell r="G10">
-            <v>0</v>
-          </cell>
-          <cell r="H10">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="B11" t="str">
-            <v>Devarapalli</v>
-          </cell>
-          <cell r="G11">
-            <v>0</v>
-          </cell>
-          <cell r="H11">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="B12" t="str">
-            <v>Golugonda</v>
-          </cell>
-          <cell r="G12">
-            <v>0</v>
-          </cell>
-          <cell r="H12">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="B13" t="str">
-            <v>K.D.Peta</v>
-          </cell>
-          <cell r="G13">
-            <v>0</v>
-          </cell>
-          <cell r="H13">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="B14" t="str">
-            <v>K.Kotapadu</v>
-          </cell>
-          <cell r="G14">
-            <v>0</v>
-          </cell>
-          <cell r="H14">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="B15" t="str">
-            <v>Kasimkota</v>
-          </cell>
-          <cell r="G15">
-            <v>0</v>
-          </cell>
-          <cell r="H15">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="B16" t="str">
-            <v>Kotavurtla</v>
-          </cell>
-          <cell r="G16">
-            <v>0</v>
-          </cell>
-          <cell r="H16">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="B17" t="str">
-            <v>Kothakota</v>
-          </cell>
-          <cell r="G17">
-            <v>0</v>
-          </cell>
-          <cell r="H17">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="B18" t="str">
-            <v>Mahila UPS, Anakapalli</v>
-          </cell>
-          <cell r="G18">
-            <v>0</v>
-          </cell>
-          <cell r="H18">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="B19" t="str">
-            <v>Makavarapalem</v>
-          </cell>
-          <cell r="G19">
-            <v>0</v>
-          </cell>
-          <cell r="H19">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="B20" t="str">
-            <v>Munagapaka</v>
-          </cell>
-          <cell r="G20">
-            <v>0</v>
-          </cell>
-          <cell r="H20">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="B21" t="str">
-            <v>Nakkapalli</v>
-          </cell>
-          <cell r="G21">
-            <v>0</v>
-          </cell>
-          <cell r="H21">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="B22" t="str">
-            <v>Narsipatnam Rural</v>
-          </cell>
-          <cell r="G22">
-            <v>0</v>
-          </cell>
-          <cell r="H22">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="B23" t="str">
-            <v>Narsipatnam Town</v>
-          </cell>
-          <cell r="G23">
-            <v>0</v>
-          </cell>
-          <cell r="H23">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="B24" t="str">
-            <v>Nathavaram</v>
-          </cell>
-          <cell r="G24">
-            <v>0</v>
-          </cell>
-          <cell r="H24">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="B25" t="str">
-            <v>Parawada</v>
-          </cell>
-          <cell r="G25">
-            <v>0</v>
-          </cell>
-          <cell r="H25">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="B26" t="str">
-            <v>Payakaraopeta</v>
-          </cell>
-          <cell r="G26">
-            <v>0</v>
-          </cell>
-          <cell r="H26">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="B27" t="str">
-            <v>Rambilli</v>
-          </cell>
-          <cell r="G27">
-            <v>0</v>
-          </cell>
-          <cell r="H27">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="B28" t="str">
-            <v>Ravikamatham</v>
-          </cell>
-          <cell r="G28">
-            <v>0</v>
-          </cell>
-          <cell r="H28">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="B29" t="str">
-            <v>Rolugunta</v>
-          </cell>
-          <cell r="G29">
-            <v>0</v>
-          </cell>
-          <cell r="H29">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="B30" t="str">
-            <v>S.Rayavaram</v>
-          </cell>
-          <cell r="G30">
-            <v>0</v>
-          </cell>
-          <cell r="H30">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="B31" t="str">
-            <v>Sabbavaram</v>
-          </cell>
-          <cell r="G31">
-            <v>0</v>
-          </cell>
-          <cell r="H31">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="B32" t="str">
-            <v>V.Madugula</v>
-          </cell>
-          <cell r="G32">
-            <v>0</v>
-          </cell>
-          <cell r="H32">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="B33" t="str">
-            <v>Yelamanchili Rural</v>
-          </cell>
-          <cell r="G33">
-            <v>0</v>
-          </cell>
-          <cell r="H33">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="B34" t="str">
-            <v>Yelamanchili Town</v>
-          </cell>
-          <cell r="G34">
-            <v>0</v>
-          </cell>
-          <cell r="H34">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="B35" t="str">
-            <v>Yelamanchili Traffic</v>
-          </cell>
-          <cell r="G35">
-            <v>0</v>
-          </cell>
-          <cell r="H35">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="C36">
-            <v>278</v>
-          </cell>
-          <cell r="D36">
-            <v>278</v>
-          </cell>
-          <cell r="E36">
-            <v>0</v>
-          </cell>
-          <cell r="F36">
-            <v>4.3828295206971681E-3</v>
-          </cell>
-          <cell r="G36" t="e">
-            <v>#DIV/0!</v>
-          </cell>
-          <cell r="H36">
-            <v>3.4914422571411872</v>
           </cell>
         </row>
       </sheetData>
@@ -19325,14 +17870,14 @@
     <tabColor rgb="FF00B0F0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Y35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:W35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.5703125" customWidth="1"/>
-    <col min="2" max="25" width="7" style="10" customWidth="1"/>
+    <col min="1" max="1" width="23.5546875" customWidth="1"/>
+    <col min="2" max="23" width="7" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="84.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" ht="84.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -19367,51 +17912,45 @@
         <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="R1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:23" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="X1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" ht="13.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>25</v>
       </c>
       <c r="B2" s="5">
         <v>2.5000000000000001E-2</v>
@@ -19444,7 +17983,7 @@
         <v>0.05</v>
       </c>
       <c r="L2" s="6">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="M2" s="6">
         <v>0.05</v>
@@ -19456,13 +17995,13 @@
         <v>0.05</v>
       </c>
       <c r="P2" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="Q2" s="6">
         <v>0.05</v>
       </c>
-      <c r="Q2" s="6">
+      <c r="R2" s="6">
         <v>0.1</v>
-      </c>
-      <c r="R2" s="6">
-        <v>0.05</v>
       </c>
       <c r="S2" s="6">
         <v>0.05</v>
@@ -19473,22 +18012,16 @@
       <c r="U2" s="6">
         <v>0.05</v>
       </c>
-      <c r="V2" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="W2" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="X2" s="5">
+      <c r="V2" s="5">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="Y2" s="5">
+      <c r="W2" s="5">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:25" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B3" s="8" t="str">
         <f>VLOOKUP(A3,'[1]1_MEDLEAPR_PME'!B:H,6,0)</f>
@@ -19531,65 +18064,56 @@
         <v>100</v>
       </c>
       <c r="L3" s="8">
-        <f>VLOOKUP(A3,'[1]11_e DAR'!B:F,4,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A3,'[1]12_CEIR'!B:L,10,0)</f>
+        <v>0</v>
       </c>
       <c r="M3" s="8">
-        <f>VLOOKUP(A3,'[1]12_CEIR'!B:L,10,0)</f>
-        <v>0</v>
-      </c>
-      <c r="N3" s="8">
         <f>VLOOKUP(A3,'[1]13_EPROSEC'!B:H,4,0)</f>
         <v>50</v>
       </c>
-      <c r="O3" s="8">
+      <c r="N3" s="8">
         <f>VLOOKUP(A3,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
         <v>91.666666666666657</v>
       </c>
+      <c r="O3" s="8">
+        <f>VLOOKUP(A3,'[1]15_EOFFICE'!B:K,9,0)</f>
+        <v>0</v>
+      </c>
       <c r="P3" s="8">
-        <f>VLOOKUP(A3,'[1]15_EOFFICE'!B:K,9,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q3" s="8">
         <f>VLOOKUP(A3,'[1]16_APOLIS'!B:K,10,0)</f>
         <v>81.818181818181813</v>
       </c>
+      <c r="Q3" s="14">
+        <v>0</v>
+      </c>
       <c r="R3" s="8">
-        <f>VLOOKUP(A3,'[1]17_DRONE_FLYING'!B:J,9,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A3,'[1]11_e DAR'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="S3" s="8">
-        <f>VLOOKUP(A3,'[1]18_112_TABS'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T3" s="8">
-        <f>VLOOKUP(A3,'[1]19_DIAL100_RES'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U3" s="8">
         <f>VLOOKUP(A3,'[1]20_CCTV_360'!B:S,17,0)</f>
         <v>71.428571428571431</v>
       </c>
+      <c r="T3" s="8">
+        <f>VLOOKUP(A3,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U3" s="8">
+        <f>VLOOKUP(A3,'[1]22_eFSL'!B:F,4,0)</f>
+        <v>100</v>
+      </c>
       <c r="V3" s="8">
-        <f>VLOOKUP(A3,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <f>VLOOKUP(A3,'[1]23_UC3'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="W3" s="8">
-        <f>VLOOKUP(A3,'[1]22_eFSL'!B:F,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="X3" s="8">
-        <f>VLOOKUP(A3,'[1]23_UC3'!B:D,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y3" s="8">
         <f>VLOOKUP(A3,'[1]23_UC4'!B:D,3,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:25" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B4" s="8">
         <f>VLOOKUP(A4,'[1]1_MEDLEAPR_PME'!B:H,6,0)</f>
@@ -19632,65 +18156,56 @@
         <v>43.065693430656935</v>
       </c>
       <c r="L4" s="8">
-        <f>VLOOKUP(A4,'[1]11_e DAR'!B:F,4,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A4,'[1]12_CEIR'!B:L,10,0)</f>
+        <v>0</v>
       </c>
       <c r="M4" s="8">
-        <f>VLOOKUP(A4,'[1]12_CEIR'!B:L,10,0)</f>
-        <v>0</v>
-      </c>
-      <c r="N4" s="8">
         <f>VLOOKUP(A4,'[1]13_EPROSEC'!B:H,4,0)</f>
         <v>33.333333333333336</v>
       </c>
-      <c r="O4" s="8">
+      <c r="N4" s="8">
         <f>VLOOKUP(A4,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
         <v>52.419510314247162</v>
       </c>
+      <c r="O4" s="8">
+        <f>VLOOKUP(A4,'[1]15_EOFFICE'!B:K,9,0)</f>
+        <v>0</v>
+      </c>
       <c r="P4" s="8">
-        <f>VLOOKUP(A4,'[1]15_EOFFICE'!B:K,9,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q4" s="8">
         <f>VLOOKUP(A4,'[1]16_APOLIS'!B:K,10,0)</f>
         <v>82.35294117647058</v>
       </c>
+      <c r="Q4" s="14">
+        <v>0</v>
+      </c>
       <c r="R4" s="8">
-        <f>VLOOKUP(A4,'[1]17_DRONE_FLYING'!B:J,9,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A4,'[1]11_e DAR'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="S4" s="8">
-        <f>VLOOKUP(A4,'[1]18_112_TABS'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T4" s="8">
-        <f>VLOOKUP(A4,'[1]19_DIAL100_RES'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U4" s="8">
         <f>VLOOKUP(A4,'[1]20_CCTV_360'!B:S,17,0)</f>
         <v>92.857142857142861</v>
       </c>
+      <c r="T4" s="8">
+        <f>VLOOKUP(A4,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U4" s="8">
+        <f>VLOOKUP(A4,'[1]22_eFSL'!B:F,4,0)</f>
+        <v>100</v>
+      </c>
       <c r="V4" s="8">
-        <f>VLOOKUP(A4,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <f>VLOOKUP(A4,'[1]23_UC3'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="W4" s="8">
-        <f>VLOOKUP(A4,'[1]22_eFSL'!B:F,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="X4" s="8">
-        <f>VLOOKUP(A4,'[1]23_UC3'!B:D,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y4" s="8">
         <f>VLOOKUP(A4,'[1]23_UC4'!B:D,3,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:25" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B5" s="8">
         <f>VLOOKUP(A5,'[1]1_MEDLEAPR_PME'!B:H,6,0)</f>
@@ -19733,65 +18248,56 @@
         <v>37.517630465444284</v>
       </c>
       <c r="L5" s="8">
-        <f>VLOOKUP(A5,'[1]11_e DAR'!B:F,4,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A5,'[1]12_CEIR'!B:L,10,0)</f>
+        <v>0</v>
       </c>
       <c r="M5" s="8">
-        <f>VLOOKUP(A5,'[1]12_CEIR'!B:L,10,0)</f>
+        <f>VLOOKUP(A5,'[1]13_EPROSEC'!B:H,4,0)</f>
         <v>0</v>
       </c>
       <c r="N5" s="8">
-        <f>VLOOKUP(A5,'[1]13_EPROSEC'!B:H,4,0)</f>
-        <v>0</v>
-      </c>
-      <c r="O5" s="8">
         <f>VLOOKUP(A5,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
         <v>50.480769230769234</v>
       </c>
+      <c r="O5" s="8">
+        <f>VLOOKUP(A5,'[1]15_EOFFICE'!B:K,9,0)</f>
+        <v>0</v>
+      </c>
       <c r="P5" s="8">
-        <f>VLOOKUP(A5,'[1]15_EOFFICE'!B:K,9,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q5" s="8">
         <f>VLOOKUP(A5,'[1]16_APOLIS'!B:K,10,0)</f>
         <v>83.333333333333329</v>
       </c>
+      <c r="Q5" s="14">
+        <v>0</v>
+      </c>
       <c r="R5" s="8">
-        <f>VLOOKUP(A5,'[1]17_DRONE_FLYING'!B:J,9,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A5,'[1]11_e DAR'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="S5" s="8">
-        <f>VLOOKUP(A5,'[1]18_112_TABS'!B:H,6,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A5,'[1]20_CCTV_360'!B:S,17,0)</f>
+        <v>100</v>
       </c>
       <c r="T5" s="8">
-        <f>VLOOKUP(A5,'[1]19_DIAL100_RES'!B:H,6,0)</f>
+        <f>VLOOKUP(A5,'[1]21_NEWS360AI'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="U5" s="8">
-        <f>VLOOKUP(A5,'[1]20_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A5,'[1]22_eFSL'!B:F,4,0)</f>
         <v>100</v>
       </c>
       <c r="V5" s="8">
-        <f>VLOOKUP(A5,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <f>VLOOKUP(A5,'[1]23_UC3'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="W5" s="8">
-        <f>VLOOKUP(A5,'[1]22_eFSL'!B:F,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="X5" s="8">
-        <f>VLOOKUP(A5,'[1]23_UC3'!B:D,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y5" s="8">
         <f>VLOOKUP(A5,'[1]23_UC4'!B:D,3,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B6" s="8" t="str">
         <f>VLOOKUP(A6,'[1]1_MEDLEAPR_PME'!B:H,6,0)</f>
@@ -19834,65 +18340,56 @@
         <v>53.879310344827587</v>
       </c>
       <c r="L6" s="8">
-        <f>VLOOKUP(A6,'[1]11_e DAR'!B:F,4,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A6,'[1]12_CEIR'!B:L,10,0)</f>
+        <v>0</v>
       </c>
       <c r="M6" s="8">
-        <f>VLOOKUP(A6,'[1]12_CEIR'!B:L,10,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A6,'[1]13_EPROSEC'!B:H,4,0)</f>
+        <v>100</v>
       </c>
       <c r="N6" s="8">
-        <f>VLOOKUP(A6,'[1]13_EPROSEC'!B:H,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="O6" s="8">
         <f>VLOOKUP(A6,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
         <v>52.463119072708118</v>
       </c>
+      <c r="O6" s="8">
+        <f>VLOOKUP(A6,'[1]15_EOFFICE'!B:K,9,0)</f>
+        <v>0</v>
+      </c>
       <c r="P6" s="8">
-        <f>VLOOKUP(A6,'[1]15_EOFFICE'!B:K,9,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q6" s="8">
         <f>VLOOKUP(A6,'[1]16_APOLIS'!B:K,10,0)</f>
         <v>83.333333333333343</v>
       </c>
+      <c r="Q6" s="14">
+        <v>0</v>
+      </c>
       <c r="R6" s="8">
-        <f>VLOOKUP(A6,'[1]17_DRONE_FLYING'!B:J,9,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A6,'[1]11_e DAR'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="S6" s="8">
-        <f>VLOOKUP(A6,'[1]18_112_TABS'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T6" s="8">
-        <f>VLOOKUP(A6,'[1]19_DIAL100_RES'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U6" s="8">
         <f>VLOOKUP(A6,'[1]20_CCTV_360'!B:S,17,0)</f>
         <v>71.428571428571431</v>
       </c>
+      <c r="T6" s="8">
+        <f>VLOOKUP(A6,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U6" s="8">
+        <f>VLOOKUP(A6,'[1]22_eFSL'!B:F,4,0)</f>
+        <v>100</v>
+      </c>
       <c r="V6" s="8">
-        <f>VLOOKUP(A6,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <f>VLOOKUP(A6,'[1]23_UC3'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="W6" s="8">
-        <f>VLOOKUP(A6,'[1]22_eFSL'!B:F,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="X6" s="8">
-        <f>VLOOKUP(A6,'[1]23_UC3'!B:D,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y6" s="8">
         <f>VLOOKUP(A6,'[1]23_UC4'!B:D,3,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:25" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B7" s="8">
         <f>VLOOKUP(A7,'[1]1_MEDLEAPR_PME'!B:H,6,0)</f>
@@ -19935,65 +18432,56 @@
         <v>52.686308492201043</v>
       </c>
       <c r="L7" s="8">
-        <f>VLOOKUP(A7,'[1]11_e DAR'!B:F,4,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A7,'[1]12_CEIR'!B:L,10,0)</f>
+        <v>0</v>
       </c>
       <c r="M7" s="8">
-        <f>VLOOKUP(A7,'[1]12_CEIR'!B:L,10,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A7,'[1]13_EPROSEC'!B:H,4,0)</f>
+        <v>100</v>
       </c>
       <c r="N7" s="8">
-        <f>VLOOKUP(A7,'[1]13_EPROSEC'!B:H,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="O7" s="8">
         <f>VLOOKUP(A7,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
         <v>93.243243243243242</v>
       </c>
+      <c r="O7" s="8">
+        <f>VLOOKUP(A7,'[1]15_EOFFICE'!B:K,9,0)</f>
+        <v>0</v>
+      </c>
       <c r="P7" s="8">
-        <f>VLOOKUP(A7,'[1]15_EOFFICE'!B:K,9,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q7" s="8">
         <f>VLOOKUP(A7,'[1]16_APOLIS'!B:K,10,0)</f>
         <v>82.35294117647058</v>
       </c>
+      <c r="Q7" s="14">
+        <v>0</v>
+      </c>
       <c r="R7" s="8">
-        <f>VLOOKUP(A7,'[1]17_DRONE_FLYING'!B:J,9,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A7,'[1]11_e DAR'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="S7" s="8">
-        <f>VLOOKUP(A7,'[1]18_112_TABS'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T7" s="8">
-        <f>VLOOKUP(A7,'[1]19_DIAL100_RES'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U7" s="8">
         <f>VLOOKUP(A7,'[1]20_CCTV_360'!B:S,17,0)</f>
         <v>28.571428571428569</v>
       </c>
+      <c r="T7" s="8">
+        <f>VLOOKUP(A7,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U7" s="8">
+        <f>VLOOKUP(A7,'[1]22_eFSL'!B:F,4,0)</f>
+        <v>100</v>
+      </c>
       <c r="V7" s="8">
-        <f>VLOOKUP(A7,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <f>VLOOKUP(A7,'[1]23_UC3'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="W7" s="8">
-        <f>VLOOKUP(A7,'[1]22_eFSL'!B:F,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="X7" s="8">
-        <f>VLOOKUP(A7,'[1]23_UC3'!B:D,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y7" s="8">
         <f>VLOOKUP(A7,'[1]23_UC4'!B:D,3,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:25" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B8" s="8">
         <f>VLOOKUP(A8,'[1]1_MEDLEAPR_PME'!B:H,6,0)</f>
@@ -20036,65 +18524,56 @@
         <v>97.368421052631575</v>
       </c>
       <c r="L8" s="8">
-        <f>VLOOKUP(A8,'[1]11_e DAR'!B:F,4,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A8,'[1]12_CEIR'!B:L,10,0)</f>
+        <v>0</v>
       </c>
       <c r="M8" s="8">
-        <f>VLOOKUP(A8,'[1]12_CEIR'!B:L,10,0)</f>
-        <v>0</v>
-      </c>
-      <c r="N8" s="8">
         <f>VLOOKUP(A8,'[1]13_EPROSEC'!B:H,4,0)</f>
         <v>50</v>
       </c>
+      <c r="N8" s="8">
+        <f>VLOOKUP(A8,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
+        <v>100</v>
+      </c>
       <c r="O8" s="8">
-        <f>VLOOKUP(A8,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A8,'[1]15_EOFFICE'!B:K,9,0)</f>
+        <v>0</v>
       </c>
       <c r="P8" s="8">
-        <f>VLOOKUP(A8,'[1]15_EOFFICE'!B:K,9,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q8" s="8">
         <f>VLOOKUP(A8,'[1]16_APOLIS'!B:K,10,0)</f>
         <v>85</v>
       </c>
+      <c r="Q8" s="14">
+        <v>0</v>
+      </c>
       <c r="R8" s="8">
-        <f>VLOOKUP(A8,'[1]17_DRONE_FLYING'!B:J,9,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A8,'[1]11_e DAR'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="S8" s="8">
-        <f>VLOOKUP(A8,'[1]18_112_TABS'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T8" s="8">
-        <f>VLOOKUP(A8,'[1]19_DIAL100_RES'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U8" s="8">
         <f>VLOOKUP(A8,'[1]20_CCTV_360'!B:S,17,0)</f>
         <v>35.714285714285715</v>
       </c>
+      <c r="T8" s="8">
+        <f>VLOOKUP(A8,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="8">
+        <f>VLOOKUP(A8,'[1]22_eFSL'!B:F,4,0)</f>
+        <v>0</v>
+      </c>
       <c r="V8" s="8">
-        <f>VLOOKUP(A8,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <f>VLOOKUP(A8,'[1]23_UC3'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="W8" s="8">
-        <f>VLOOKUP(A8,'[1]22_eFSL'!B:F,4,0)</f>
-        <v>0</v>
-      </c>
-      <c r="X8" s="8">
-        <f>VLOOKUP(A8,'[1]23_UC3'!B:D,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y8" s="8">
         <f>VLOOKUP(A8,'[1]23_UC4'!B:D,3,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:25" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B9" s="8" t="str">
         <f>VLOOKUP(A9,'[1]1_MEDLEAPR_PME'!B:H,6,0)</f>
@@ -20137,65 +18616,56 @@
         <v>98.181818181818187</v>
       </c>
       <c r="L9" s="8">
-        <f>VLOOKUP(A9,'[1]11_e DAR'!B:F,4,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A9,'[1]12_CEIR'!B:L,10,0)</f>
+        <v>0</v>
       </c>
       <c r="M9" s="8">
-        <f>VLOOKUP(A9,'[1]12_CEIR'!B:L,10,0)</f>
-        <v>0</v>
-      </c>
-      <c r="N9" s="8">
         <f>VLOOKUP(A9,'[1]13_EPROSEC'!B:H,4,0)</f>
         <v>50</v>
       </c>
+      <c r="N9" s="8">
+        <f>VLOOKUP(A9,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
+        <v>100</v>
+      </c>
       <c r="O9" s="8">
-        <f>VLOOKUP(A9,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A9,'[1]15_EOFFICE'!B:K,9,0)</f>
+        <v>0</v>
       </c>
       <c r="P9" s="8">
-        <f>VLOOKUP(A9,'[1]15_EOFFICE'!B:K,9,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q9" s="8">
         <f>VLOOKUP(A9,'[1]16_APOLIS'!B:K,10,0)</f>
         <v>83.333333333333343</v>
       </c>
+      <c r="Q9" s="14">
+        <v>0</v>
+      </c>
       <c r="R9" s="8">
-        <f>VLOOKUP(A9,'[1]17_DRONE_FLYING'!B:J,9,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A9,'[1]11_e DAR'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="S9" s="8">
-        <f>VLOOKUP(A9,'[1]18_112_TABS'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T9" s="8">
-        <f>VLOOKUP(A9,'[1]19_DIAL100_RES'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U9" s="8">
         <f>VLOOKUP(A9,'[1]20_CCTV_360'!B:S,17,0)</f>
         <v>7.1428571428571423</v>
       </c>
+      <c r="T9" s="8">
+        <f>VLOOKUP(A9,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U9" s="8">
+        <f>VLOOKUP(A9,'[1]22_eFSL'!B:F,4,0)</f>
+        <v>100</v>
+      </c>
       <c r="V9" s="8">
-        <f>VLOOKUP(A9,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <f>VLOOKUP(A9,'[1]23_UC3'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="W9" s="8">
-        <f>VLOOKUP(A9,'[1]22_eFSL'!B:F,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="X9" s="8">
-        <f>VLOOKUP(A9,'[1]23_UC3'!B:D,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y9" s="8">
         <f>VLOOKUP(A9,'[1]23_UC4'!B:D,3,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:25" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B10" s="8" t="str">
         <f>VLOOKUP(A10,'[1]1_MEDLEAPR_PME'!B:H,6,0)</f>
@@ -20238,65 +18708,56 @@
         <v>71.712538226299699</v>
       </c>
       <c r="L10" s="8">
-        <f>VLOOKUP(A10,'[1]11_e DAR'!B:F,4,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A10,'[1]12_CEIR'!B:L,10,0)</f>
+        <v>0</v>
       </c>
       <c r="M10" s="8">
-        <f>VLOOKUP(A10,'[1]12_CEIR'!B:L,10,0)</f>
-        <v>0</v>
-      </c>
-      <c r="N10" s="8">
         <f>VLOOKUP(A10,'[1]13_EPROSEC'!B:H,4,0)</f>
         <v>66.666666666666671</v>
       </c>
-      <c r="O10" s="8">
+      <c r="N10" s="8">
         <f>VLOOKUP(A10,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
         <v>96.928104575163388</v>
       </c>
+      <c r="O10" s="8">
+        <f>VLOOKUP(A10,'[1]15_EOFFICE'!B:K,9,0)</f>
+        <v>0</v>
+      </c>
       <c r="P10" s="8">
-        <f>VLOOKUP(A10,'[1]15_EOFFICE'!B:K,9,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q10" s="8">
         <f>VLOOKUP(A10,'[1]16_APOLIS'!B:K,10,0)</f>
         <v>82.5</v>
       </c>
+      <c r="Q10" s="14">
+        <v>0</v>
+      </c>
       <c r="R10" s="8">
-        <f>VLOOKUP(A10,'[1]17_DRONE_FLYING'!B:J,9,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A10,'[1]11_e DAR'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="S10" s="8">
-        <f>VLOOKUP(A10,'[1]18_112_TABS'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T10" s="8">
-        <f>VLOOKUP(A10,'[1]19_DIAL100_RES'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U10" s="8">
         <f>VLOOKUP(A10,'[1]20_CCTV_360'!B:S,17,0)</f>
         <v>71.428571428571431</v>
       </c>
+      <c r="T10" s="8">
+        <f>VLOOKUP(A10,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U10" s="8">
+        <f>VLOOKUP(A10,'[1]22_eFSL'!B:F,4,0)</f>
+        <v>100</v>
+      </c>
       <c r="V10" s="8">
-        <f>VLOOKUP(A10,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <f>VLOOKUP(A10,'[1]23_UC3'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="W10" s="8">
-        <f>VLOOKUP(A10,'[1]22_eFSL'!B:F,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="X10" s="8">
-        <f>VLOOKUP(A10,'[1]23_UC3'!B:D,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y10" s="8">
         <f>VLOOKUP(A10,'[1]23_UC4'!B:D,3,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:25" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B11" s="8" t="str">
         <f>VLOOKUP(A11,'[1]1_MEDLEAPR_PME'!B:H,6,0)</f>
@@ -20339,65 +18800,56 @@
         <v>85.31073446327683</v>
       </c>
       <c r="L11" s="8">
-        <f>VLOOKUP(A11,'[1]11_e DAR'!B:F,4,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A11,'[1]12_CEIR'!B:L,10,0)</f>
+        <v>0</v>
       </c>
       <c r="M11" s="8">
-        <f>VLOOKUP(A11,'[1]12_CEIR'!B:L,10,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A11,'[1]13_EPROSEC'!B:H,4,0)</f>
+        <v>100</v>
       </c>
       <c r="N11" s="8">
-        <f>VLOOKUP(A11,'[1]13_EPROSEC'!B:H,4,0)</f>
+        <f>VLOOKUP(A11,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
         <v>100</v>
       </c>
       <c r="O11" s="8">
-        <f>VLOOKUP(A11,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A11,'[1]15_EOFFICE'!B:K,9,0)</f>
+        <v>0</v>
       </c>
       <c r="P11" s="8">
-        <f>VLOOKUP(A11,'[1]15_EOFFICE'!B:K,9,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q11" s="8">
         <f>VLOOKUP(A11,'[1]16_APOLIS'!B:K,10,0)</f>
         <v>85</v>
       </c>
+      <c r="Q11" s="14">
+        <v>0</v>
+      </c>
       <c r="R11" s="8">
-        <f>VLOOKUP(A11,'[1]17_DRONE_FLYING'!B:J,9,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A11,'[1]11_e DAR'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="S11" s="8">
-        <f>VLOOKUP(A11,'[1]18_112_TABS'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T11" s="8">
-        <f>VLOOKUP(A11,'[1]19_DIAL100_RES'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U11" s="8">
         <f>VLOOKUP(A11,'[1]20_CCTV_360'!B:S,17,0)</f>
         <v>14.285714285714285</v>
       </c>
+      <c r="T11" s="8">
+        <f>VLOOKUP(A11,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U11" s="8">
+        <f>VLOOKUP(A11,'[1]22_eFSL'!B:F,4,0)</f>
+        <v>100</v>
+      </c>
       <c r="V11" s="8">
-        <f>VLOOKUP(A11,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <f>VLOOKUP(A11,'[1]23_UC3'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="W11" s="8">
-        <f>VLOOKUP(A11,'[1]22_eFSL'!B:F,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="X11" s="8">
-        <f>VLOOKUP(A11,'[1]23_UC3'!B:D,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y11" s="8">
         <f>VLOOKUP(A11,'[1]23_UC4'!B:D,3,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:25" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B12" s="8">
         <f>VLOOKUP(A12,'[1]1_MEDLEAPR_PME'!B:H,6,0)</f>
@@ -20440,65 +18892,56 @@
         <v>61.302681992337163</v>
       </c>
       <c r="L12" s="8">
-        <f>VLOOKUP(A12,'[1]11_e DAR'!B:F,4,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A12,'[1]12_CEIR'!B:L,10,0)</f>
+        <v>0</v>
       </c>
       <c r="M12" s="8">
-        <f>VLOOKUP(A12,'[1]12_CEIR'!B:L,10,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A12,'[1]13_EPROSEC'!B:H,4,0)</f>
+        <v>100</v>
       </c>
       <c r="N12" s="8">
-        <f>VLOOKUP(A12,'[1]13_EPROSEC'!B:H,4,0)</f>
+        <f>VLOOKUP(A12,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
         <v>100</v>
       </c>
       <c r="O12" s="8">
-        <f>VLOOKUP(A12,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A12,'[1]15_EOFFICE'!B:K,9,0)</f>
+        <v>0</v>
       </c>
       <c r="P12" s="8">
-        <f>VLOOKUP(A12,'[1]15_EOFFICE'!B:K,9,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q12" s="8">
         <f>VLOOKUP(A12,'[1]16_APOLIS'!B:K,10,0)</f>
         <v>85</v>
       </c>
+      <c r="Q12" s="14">
+        <v>0</v>
+      </c>
       <c r="R12" s="8">
-        <f>VLOOKUP(A12,'[1]17_DRONE_FLYING'!B:J,9,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A12,'[1]11_e DAR'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="S12" s="8">
-        <f>VLOOKUP(A12,'[1]18_112_TABS'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T12" s="8">
-        <f>VLOOKUP(A12,'[1]19_DIAL100_RES'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U12" s="8">
         <f>VLOOKUP(A12,'[1]20_CCTV_360'!B:S,17,0)</f>
         <v>78.571428571428569</v>
       </c>
+      <c r="T12" s="8">
+        <f>VLOOKUP(A12,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U12" s="8">
+        <f>VLOOKUP(A12,'[1]22_eFSL'!B:F,4,0)</f>
+        <v>0</v>
+      </c>
       <c r="V12" s="8">
-        <f>VLOOKUP(A12,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <f>VLOOKUP(A12,'[1]23_UC3'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="W12" s="8">
-        <f>VLOOKUP(A12,'[1]22_eFSL'!B:F,4,0)</f>
-        <v>0</v>
-      </c>
-      <c r="X12" s="8">
-        <f>VLOOKUP(A12,'[1]23_UC3'!B:D,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y12" s="8">
         <f>VLOOKUP(A12,'[1]23_UC4'!B:D,3,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:25" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B13" s="8" t="str">
         <f>VLOOKUP(A13,'[1]1_MEDLEAPR_PME'!B:H,6,0)</f>
@@ -20541,65 +18984,56 @@
         <v>89.325842696629209</v>
       </c>
       <c r="L13" s="8">
-        <f>VLOOKUP(A13,'[1]11_e DAR'!B:F,4,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A13,'[1]12_CEIR'!B:L,10,0)</f>
+        <v>0</v>
       </c>
       <c r="M13" s="8">
-        <f>VLOOKUP(A13,'[1]12_CEIR'!B:L,10,0)</f>
+        <f>VLOOKUP(A13,'[1]13_EPROSEC'!B:H,4,0)</f>
         <v>0</v>
       </c>
       <c r="N13" s="8">
-        <f>VLOOKUP(A13,'[1]13_EPROSEC'!B:H,4,0)</f>
-        <v>0</v>
-      </c>
-      <c r="O13" s="8">
         <f>VLOOKUP(A13,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
         <v>95.833333333333343</v>
       </c>
+      <c r="O13" s="8">
+        <f>VLOOKUP(A13,'[1]15_EOFFICE'!B:K,9,0)</f>
+        <v>0</v>
+      </c>
       <c r="P13" s="8">
-        <f>VLOOKUP(A13,'[1]15_EOFFICE'!B:K,9,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q13" s="8">
         <f>VLOOKUP(A13,'[1]16_APOLIS'!B:K,10,0)</f>
         <v>81.25</v>
       </c>
+      <c r="Q13" s="14">
+        <v>0</v>
+      </c>
       <c r="R13" s="8">
-        <f>VLOOKUP(A13,'[1]17_DRONE_FLYING'!B:J,9,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A13,'[1]11_e DAR'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="S13" s="8">
-        <f>VLOOKUP(A13,'[1]18_112_TABS'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T13" s="8">
-        <f>VLOOKUP(A13,'[1]19_DIAL100_RES'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U13" s="8">
         <f>VLOOKUP(A13,'[1]20_CCTV_360'!B:S,17,0)</f>
         <v>7.1428571428571423</v>
       </c>
+      <c r="T13" s="8">
+        <f>VLOOKUP(A13,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U13" s="8">
+        <f>VLOOKUP(A13,'[1]22_eFSL'!B:F,4,0)</f>
+        <v>100</v>
+      </c>
       <c r="V13" s="8">
-        <f>VLOOKUP(A13,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <f>VLOOKUP(A13,'[1]23_UC3'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="W13" s="8">
-        <f>VLOOKUP(A13,'[1]22_eFSL'!B:F,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="X13" s="8">
-        <f>VLOOKUP(A13,'[1]23_UC3'!B:D,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y13" s="8">
         <f>VLOOKUP(A13,'[1]23_UC4'!B:D,3,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:25" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B14" s="8">
         <f>VLOOKUP(A14,'[1]1_MEDLEAPR_PME'!B:H,6,0)</f>
@@ -20642,65 +19076,56 @@
         <v>73.913043478260875</v>
       </c>
       <c r="L14" s="8">
-        <f>VLOOKUP(A14,'[1]11_e DAR'!B:F,4,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A14,'[1]12_CEIR'!B:L,10,0)</f>
+        <v>0</v>
       </c>
       <c r="M14" s="8">
-        <f>VLOOKUP(A14,'[1]12_CEIR'!B:L,10,0)</f>
+        <f>VLOOKUP(A14,'[1]13_EPROSEC'!B:H,4,0)</f>
         <v>0</v>
       </c>
       <c r="N14" s="8">
-        <f>VLOOKUP(A14,'[1]13_EPROSEC'!B:H,4,0)</f>
-        <v>0</v>
-      </c>
-      <c r="O14" s="8">
         <f>VLOOKUP(A14,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
         <v>92.857142857142861</v>
       </c>
+      <c r="O14" s="8">
+        <f>VLOOKUP(A14,'[1]15_EOFFICE'!B:K,9,0)</f>
+        <v>0</v>
+      </c>
       <c r="P14" s="8">
-        <f>VLOOKUP(A14,'[1]15_EOFFICE'!B:K,9,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="8">
         <f>VLOOKUP(A14,'[1]16_APOLIS'!B:K,10,0)</f>
         <v>80</v>
       </c>
+      <c r="Q14" s="14">
+        <v>0</v>
+      </c>
       <c r="R14" s="8">
-        <f>VLOOKUP(A14,'[1]17_DRONE_FLYING'!B:J,9,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A14,'[1]11_e DAR'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="S14" s="8">
-        <f>VLOOKUP(A14,'[1]18_112_TABS'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T14" s="8">
-        <f>VLOOKUP(A14,'[1]19_DIAL100_RES'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U14" s="8">
         <f>VLOOKUP(A14,'[1]20_CCTV_360'!B:S,17,0)</f>
         <v>7.1428571428571423</v>
       </c>
+      <c r="T14" s="8">
+        <f>VLOOKUP(A14,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U14" s="8">
+        <f>VLOOKUP(A14,'[1]22_eFSL'!B:F,4,0)</f>
+        <v>0</v>
+      </c>
       <c r="V14" s="8">
-        <f>VLOOKUP(A14,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <f>VLOOKUP(A14,'[1]23_UC3'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="W14" s="8">
-        <f>VLOOKUP(A14,'[1]22_eFSL'!B:F,4,0)</f>
-        <v>0</v>
-      </c>
-      <c r="X14" s="8">
-        <f>VLOOKUP(A14,'[1]23_UC3'!B:D,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y14" s="8">
         <f>VLOOKUP(A14,'[1]23_UC4'!B:D,3,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:25" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B15" s="8" t="str">
         <f>VLOOKUP(A15,'[1]1_MEDLEAPR_PME'!B:H,6,0)</f>
@@ -20743,65 +19168,56 @@
         <v>62.174578866768762</v>
       </c>
       <c r="L15" s="8">
-        <f>VLOOKUP(A15,'[1]11_e DAR'!B:F,4,0)</f>
+        <f>VLOOKUP(A15,'[1]12_CEIR'!B:L,10,0)</f>
         <v>0</v>
       </c>
       <c r="M15" s="8">
-        <f>VLOOKUP(A15,'[1]12_CEIR'!B:L,10,0)</f>
-        <v>0</v>
-      </c>
-      <c r="N15" s="8">
         <f>VLOOKUP(A15,'[1]13_EPROSEC'!B:H,4,0)</f>
         <v>20</v>
       </c>
-      <c r="O15" s="8">
+      <c r="N15" s="8">
         <f>VLOOKUP(A15,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
         <v>51.135295959912312</v>
       </c>
+      <c r="O15" s="8">
+        <f>VLOOKUP(A15,'[1]15_EOFFICE'!B:K,9,0)</f>
+        <v>0</v>
+      </c>
       <c r="P15" s="8">
-        <f>VLOOKUP(A15,'[1]15_EOFFICE'!B:K,9,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="8">
         <f>VLOOKUP(A15,'[1]16_APOLIS'!B:K,10,0)</f>
         <v>85</v>
       </c>
+      <c r="Q15" s="14">
+        <v>0</v>
+      </c>
       <c r="R15" s="8">
-        <f>VLOOKUP(A15,'[1]17_DRONE_FLYING'!B:J,9,0)</f>
+        <f>VLOOKUP(A15,'[1]11_e DAR'!B:F,4,0)</f>
         <v>0</v>
       </c>
       <c r="S15" s="8">
-        <f>VLOOKUP(A15,'[1]18_112_TABS'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T15" s="8">
-        <f>VLOOKUP(A15,'[1]19_DIAL100_RES'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U15" s="8">
         <f>VLOOKUP(A15,'[1]20_CCTV_360'!B:S,17,0)</f>
         <v>64.285714285714292</v>
       </c>
+      <c r="T15" s="8">
+        <f>VLOOKUP(A15,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U15" s="8">
+        <f>VLOOKUP(A15,'[1]22_eFSL'!B:F,4,0)</f>
+        <v>100</v>
+      </c>
       <c r="V15" s="8">
-        <f>VLOOKUP(A15,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <f>VLOOKUP(A15,'[1]23_UC3'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="W15" s="8">
-        <f>VLOOKUP(A15,'[1]22_eFSL'!B:F,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="X15" s="8">
-        <f>VLOOKUP(A15,'[1]23_UC3'!B:D,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y15" s="8">
         <f>VLOOKUP(A15,'[1]23_UC4'!B:D,3,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:25" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B16" s="8" t="str">
         <f>VLOOKUP(A16,'[1]1_MEDLEAPR_PME'!B:H,6,0)</f>
@@ -20844,65 +19260,56 @@
         <v>100</v>
       </c>
       <c r="L16" s="8">
-        <f>VLOOKUP(A16,'[1]11_e DAR'!B:F,4,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A16,'[1]12_CEIR'!B:L,10,0)</f>
+        <v>0</v>
       </c>
       <c r="M16" s="8">
-        <f>VLOOKUP(A16,'[1]12_CEIR'!B:L,10,0)</f>
-        <v>0</v>
-      </c>
-      <c r="N16" s="8">
         <f>VLOOKUP(A16,'[1]13_EPROSEC'!B:H,4,0)</f>
         <v>50</v>
       </c>
+      <c r="N16" s="8">
+        <f>VLOOKUP(A16,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
+        <v>100</v>
+      </c>
       <c r="O16" s="8">
-        <f>VLOOKUP(A16,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A16,'[1]15_EOFFICE'!B:K,9,0)</f>
+        <v>0</v>
       </c>
       <c r="P16" s="8">
-        <f>VLOOKUP(A16,'[1]15_EOFFICE'!B:K,9,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="8">
         <f>VLOOKUP(A16,'[1]16_APOLIS'!B:K,10,0)</f>
         <v>85</v>
       </c>
+      <c r="Q16" s="14">
+        <v>0</v>
+      </c>
       <c r="R16" s="8">
-        <f>VLOOKUP(A16,'[1]17_DRONE_FLYING'!B:J,9,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A16,'[1]11_e DAR'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="S16" s="8">
-        <f>VLOOKUP(A16,'[1]18_112_TABS'!B:H,6,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A16,'[1]20_CCTV_360'!B:S,17,0)</f>
+        <v>100</v>
       </c>
       <c r="T16" s="8">
-        <f>VLOOKUP(A16,'[1]19_DIAL100_RES'!B:H,6,0)</f>
+        <f>VLOOKUP(A16,'[1]21_NEWS360AI'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="U16" s="8">
-        <f>VLOOKUP(A16,'[1]20_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A16,'[1]22_eFSL'!B:F,4,0)</f>
         <v>100</v>
       </c>
       <c r="V16" s="8">
-        <f>VLOOKUP(A16,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <f>VLOOKUP(A16,'[1]23_UC3'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="W16" s="8">
-        <f>VLOOKUP(A16,'[1]22_eFSL'!B:F,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="X16" s="8">
-        <f>VLOOKUP(A16,'[1]23_UC3'!B:D,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y16" s="8">
         <f>VLOOKUP(A16,'[1]23_UC4'!B:D,3,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:25" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B17" s="8" t="str">
         <f>VLOOKUP(A17,'[1]1_MEDLEAPR_PME'!B:H,6,0)</f>
@@ -20945,65 +19352,56 @@
         <v>51.308900523560212</v>
       </c>
       <c r="L17" s="8">
-        <f>VLOOKUP(A17,'[1]11_e DAR'!B:F,4,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A17,'[1]12_CEIR'!B:L,10,0)</f>
+        <v>0</v>
       </c>
       <c r="M17" s="8">
-        <f>VLOOKUP(A17,'[1]12_CEIR'!B:L,10,0)</f>
+        <f>VLOOKUP(A17,'[1]13_EPROSEC'!B:H,4,0)</f>
         <v>0</v>
       </c>
       <c r="N17" s="8">
-        <f>VLOOKUP(A17,'[1]13_EPROSEC'!B:H,4,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A17,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
+        <v>100</v>
       </c>
       <c r="O17" s="8">
-        <f>VLOOKUP(A17,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A17,'[1]15_EOFFICE'!B:K,9,0)</f>
+        <v>0</v>
       </c>
       <c r="P17" s="8">
-        <f>VLOOKUP(A17,'[1]15_EOFFICE'!B:K,9,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="8">
         <f>VLOOKUP(A17,'[1]16_APOLIS'!B:K,10,0)</f>
         <v>81.25</v>
       </c>
+      <c r="Q17" s="14">
+        <v>0</v>
+      </c>
       <c r="R17" s="8">
-        <f>VLOOKUP(A17,'[1]17_DRONE_FLYING'!B:J,9,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A17,'[1]11_e DAR'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="S17" s="8">
-        <f>VLOOKUP(A17,'[1]18_112_TABS'!B:H,6,0)</f>
+        <f>VLOOKUP(A17,'[1]20_CCTV_360'!B:S,17,0)</f>
         <v>0</v>
       </c>
       <c r="T17" s="8">
-        <f>VLOOKUP(A17,'[1]19_DIAL100_RES'!B:H,6,0)</f>
+        <f>VLOOKUP(A17,'[1]21_NEWS360AI'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="U17" s="8">
-        <f>VLOOKUP(A17,'[1]20_CCTV_360'!B:S,17,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A17,'[1]22_eFSL'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="V17" s="8">
-        <f>VLOOKUP(A17,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <f>VLOOKUP(A17,'[1]23_UC3'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="W17" s="8">
-        <f>VLOOKUP(A17,'[1]22_eFSL'!B:F,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="X17" s="8">
-        <f>VLOOKUP(A17,'[1]23_UC3'!B:D,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y17" s="8">
         <f>VLOOKUP(A17,'[1]23_UC4'!B:D,3,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:25" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B18" s="8" t="str">
         <f>VLOOKUP(A18,'[1]1_MEDLEAPR_PME'!B:H,6,0)</f>
@@ -21046,65 +19444,56 @@
         <v>34.042553191489361</v>
       </c>
       <c r="L18" s="8">
-        <f>VLOOKUP(A18,'[1]11_e DAR'!B:F,4,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A18,'[1]12_CEIR'!B:L,10,0)</f>
+        <v>0</v>
       </c>
       <c r="M18" s="8">
-        <f>VLOOKUP(A18,'[1]12_CEIR'!B:L,10,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A18,'[1]13_EPROSEC'!B:H,4,0)</f>
+        <v>100</v>
       </c>
       <c r="N18" s="8">
-        <f>VLOOKUP(A18,'[1]13_EPROSEC'!B:H,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="O18" s="8">
         <f>VLOOKUP(A18,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
         <v>56.756756756756758</v>
       </c>
+      <c r="O18" s="8">
+        <f>VLOOKUP(A18,'[1]15_EOFFICE'!B:K,9,0)</f>
+        <v>0</v>
+      </c>
       <c r="P18" s="8">
-        <f>VLOOKUP(A18,'[1]15_EOFFICE'!B:K,9,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="8">
         <f>VLOOKUP(A18,'[1]16_APOLIS'!B:K,10,0)</f>
         <v>83.333333333333343</v>
       </c>
+      <c r="Q18" s="14">
+        <v>0</v>
+      </c>
       <c r="R18" s="8">
-        <f>VLOOKUP(A18,'[1]17_DRONE_FLYING'!B:J,9,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A18,'[1]11_e DAR'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="S18" s="8">
-        <f>VLOOKUP(A18,'[1]18_112_TABS'!B:H,6,0)</f>
+        <f>VLOOKUP(A18,'[1]20_CCTV_360'!B:S,17,0)</f>
         <v>0</v>
       </c>
       <c r="T18" s="8">
-        <f>VLOOKUP(A18,'[1]19_DIAL100_RES'!B:H,6,0)</f>
+        <f>VLOOKUP(A18,'[1]21_NEWS360AI'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="U18" s="8">
-        <f>VLOOKUP(A18,'[1]20_CCTV_360'!B:S,17,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A18,'[1]22_eFSL'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="V18" s="8">
-        <f>VLOOKUP(A18,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <f>VLOOKUP(A18,'[1]23_UC3'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="W18" s="8">
-        <f>VLOOKUP(A18,'[1]22_eFSL'!B:F,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="X18" s="8">
-        <f>VLOOKUP(A18,'[1]23_UC3'!B:D,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y18" s="8">
         <f>VLOOKUP(A18,'[1]23_UC4'!B:D,3,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:25" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B19" s="8">
         <f>VLOOKUP(A19,'[1]1_MEDLEAPR_PME'!B:H,6,0)</f>
@@ -21147,65 +19536,56 @@
         <v>77.545691906005217</v>
       </c>
       <c r="L19" s="8">
-        <f>VLOOKUP(A19,'[1]11_e DAR'!B:F,4,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A19,'[1]12_CEIR'!B:L,10,0)</f>
+        <v>0</v>
       </c>
       <c r="M19" s="8">
-        <f>VLOOKUP(A19,'[1]12_CEIR'!B:L,10,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A19,'[1]13_EPROSEC'!B:H,4,0)</f>
+        <v>100</v>
       </c>
       <c r="N19" s="8">
-        <f>VLOOKUP(A19,'[1]13_EPROSEC'!B:H,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="O19" s="8">
         <f>VLOOKUP(A19,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
         <v>97.413793103448285</v>
       </c>
+      <c r="O19" s="8">
+        <f>VLOOKUP(A19,'[1]15_EOFFICE'!B:K,9,0)</f>
+        <v>0</v>
+      </c>
       <c r="P19" s="8">
-        <f>VLOOKUP(A19,'[1]15_EOFFICE'!B:K,9,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q19" s="8">
         <f>VLOOKUP(A19,'[1]16_APOLIS'!B:K,10,0)</f>
         <v>83.333333333333343</v>
       </c>
+      <c r="Q19" s="14">
+        <v>0</v>
+      </c>
       <c r="R19" s="8">
-        <f>VLOOKUP(A19,'[1]17_DRONE_FLYING'!B:J,9,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A19,'[1]11_e DAR'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="S19" s="8">
-        <f>VLOOKUP(A19,'[1]18_112_TABS'!B:H,6,0)</f>
+        <f>VLOOKUP(A19,'[1]20_CCTV_360'!B:S,17,0)</f>
         <v>0</v>
       </c>
       <c r="T19" s="8">
-        <f>VLOOKUP(A19,'[1]19_DIAL100_RES'!B:H,6,0)</f>
+        <f>VLOOKUP(A19,'[1]21_NEWS360AI'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="U19" s="8">
-        <f>VLOOKUP(A19,'[1]20_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A19,'[1]22_eFSL'!B:F,4,0)</f>
         <v>0</v>
       </c>
       <c r="V19" s="8">
-        <f>VLOOKUP(A19,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <f>VLOOKUP(A19,'[1]23_UC3'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="W19" s="8">
-        <f>VLOOKUP(A19,'[1]22_eFSL'!B:F,4,0)</f>
-        <v>0</v>
-      </c>
-      <c r="X19" s="8">
-        <f>VLOOKUP(A19,'[1]23_UC3'!B:D,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y19" s="8">
         <f>VLOOKUP(A19,'[1]23_UC4'!B:D,3,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:25" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B20" s="8" t="str">
         <f>VLOOKUP(A20,'[1]1_MEDLEAPR_PME'!B:H,6,0)</f>
@@ -21248,65 +19628,56 @@
         <v>52.336448598130843</v>
       </c>
       <c r="L20" s="8">
-        <f>VLOOKUP(A20,'[1]11_e DAR'!B:F,4,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A20,'[1]12_CEIR'!B:L,10,0)</f>
+        <v>0</v>
       </c>
       <c r="M20" s="8">
-        <f>VLOOKUP(A20,'[1]12_CEIR'!B:L,10,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A20,'[1]13_EPROSEC'!B:H,4,0)</f>
+        <v>100</v>
       </c>
       <c r="N20" s="8">
-        <f>VLOOKUP(A20,'[1]13_EPROSEC'!B:H,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="O20" s="8">
         <f>VLOOKUP(A20,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
         <v>51.567749160134383</v>
       </c>
+      <c r="O20" s="8">
+        <f>VLOOKUP(A20,'[1]15_EOFFICE'!B:K,9,0)</f>
+        <v>0</v>
+      </c>
       <c r="P20" s="8">
-        <f>VLOOKUP(A20,'[1]15_EOFFICE'!B:K,9,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q20" s="8">
         <f>VLOOKUP(A20,'[1]16_APOLIS'!B:K,10,0)</f>
         <v>83.333333333333343</v>
       </c>
+      <c r="Q20" s="14">
+        <v>0</v>
+      </c>
       <c r="R20" s="8">
-        <f>VLOOKUP(A20,'[1]17_DRONE_FLYING'!B:J,9,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A20,'[1]11_e DAR'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="S20" s="8">
-        <f>VLOOKUP(A20,'[1]18_112_TABS'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T20" s="8">
-        <f>VLOOKUP(A20,'[1]19_DIAL100_RES'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U20" s="8">
         <f>VLOOKUP(A20,'[1]20_CCTV_360'!B:S,17,0)</f>
         <v>71.428571428571431</v>
       </c>
+      <c r="T20" s="8">
+        <f>VLOOKUP(A20,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U20" s="8">
+        <f>VLOOKUP(A20,'[1]22_eFSL'!B:F,4,0)</f>
+        <v>100</v>
+      </c>
       <c r="V20" s="8">
-        <f>VLOOKUP(A20,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <f>VLOOKUP(A20,'[1]23_UC3'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="W20" s="8">
-        <f>VLOOKUP(A20,'[1]22_eFSL'!B:F,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="X20" s="8">
-        <f>VLOOKUP(A20,'[1]23_UC3'!B:D,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y20" s="8">
         <f>VLOOKUP(A20,'[1]23_UC4'!B:D,3,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:25" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B21" s="8">
         <f>VLOOKUP(A21,'[1]1_MEDLEAPR_PME'!B:H,6,0)</f>
@@ -21349,65 +19720,56 @@
         <v>94.555353901996369</v>
       </c>
       <c r="L21" s="8">
-        <f>VLOOKUP(A21,'[1]11_e DAR'!B:F,4,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A21,'[1]12_CEIR'!B:L,10,0)</f>
+        <v>0</v>
       </c>
       <c r="M21" s="8">
-        <f>VLOOKUP(A21,'[1]12_CEIR'!B:L,10,0)</f>
-        <v>0</v>
-      </c>
-      <c r="N21" s="8">
         <f>VLOOKUP(A21,'[1]13_EPROSEC'!B:H,4,0)</f>
         <v>33.333333333333336</v>
       </c>
-      <c r="O21" s="8">
+      <c r="N21" s="8">
         <f>VLOOKUP(A21,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
         <v>98.607142857142861</v>
       </c>
+      <c r="O21" s="8">
+        <f>VLOOKUP(A21,'[1]15_EOFFICE'!B:K,9,0)</f>
+        <v>0</v>
+      </c>
       <c r="P21" s="8">
-        <f>VLOOKUP(A21,'[1]15_EOFFICE'!B:K,9,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q21" s="8">
         <f>VLOOKUP(A21,'[1]16_APOLIS'!B:K,10,0)</f>
         <v>85</v>
       </c>
+      <c r="Q21" s="14">
+        <v>0</v>
+      </c>
       <c r="R21" s="8">
-        <f>VLOOKUP(A21,'[1]17_DRONE_FLYING'!B:J,9,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A21,'[1]11_e DAR'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="S21" s="8">
-        <f>VLOOKUP(A21,'[1]18_112_TABS'!B:H,6,0)</f>
+        <f>VLOOKUP(A21,'[1]20_CCTV_360'!B:S,17,0)</f>
         <v>0</v>
       </c>
       <c r="T21" s="8">
-        <f>VLOOKUP(A21,'[1]19_DIAL100_RES'!B:H,6,0)</f>
+        <f>VLOOKUP(A21,'[1]21_NEWS360AI'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="U21" s="8">
-        <f>VLOOKUP(A21,'[1]20_CCTV_360'!B:S,17,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A21,'[1]22_eFSL'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="V21" s="8">
-        <f>VLOOKUP(A21,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <f>VLOOKUP(A21,'[1]23_UC3'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="W21" s="8">
-        <f>VLOOKUP(A21,'[1]22_eFSL'!B:F,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="X21" s="8">
-        <f>VLOOKUP(A21,'[1]23_UC3'!B:D,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y21" s="8">
         <f>VLOOKUP(A21,'[1]23_UC4'!B:D,3,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:25" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B22" s="8" t="str">
         <f>VLOOKUP(A22,'[1]1_MEDLEAPR_PME'!B:H,6,0)</f>
@@ -21450,65 +19812,56 @@
         <v>71.171171171171167</v>
       </c>
       <c r="L22" s="8">
-        <f>VLOOKUP(A22,'[1]11_e DAR'!B:F,4,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A22,'[1]12_CEIR'!B:L,10,0)</f>
+        <v>0</v>
       </c>
       <c r="M22" s="8">
-        <f>VLOOKUP(A22,'[1]12_CEIR'!B:L,10,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A22,'[1]13_EPROSEC'!B:H,4,0)</f>
+        <v>100</v>
       </c>
       <c r="N22" s="8">
-        <f>VLOOKUP(A22,'[1]13_EPROSEC'!B:H,4,0)</f>
+        <f>VLOOKUP(A22,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
         <v>100</v>
       </c>
       <c r="O22" s="8">
-        <f>VLOOKUP(A22,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A22,'[1]15_EOFFICE'!B:K,9,0)</f>
+        <v>0</v>
       </c>
       <c r="P22" s="8">
-        <f>VLOOKUP(A22,'[1]15_EOFFICE'!B:K,9,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="8">
         <f>VLOOKUP(A22,'[1]16_APOLIS'!B:K,10,0)</f>
         <v>83.333333333333343</v>
       </c>
+      <c r="Q22" s="14">
+        <v>0</v>
+      </c>
       <c r="R22" s="8">
-        <f>VLOOKUP(A22,'[1]17_DRONE_FLYING'!B:J,9,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A22,'[1]11_e DAR'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="S22" s="8">
-        <f>VLOOKUP(A22,'[1]18_112_TABS'!B:H,6,0)</f>
+        <f>VLOOKUP(A22,'[1]20_CCTV_360'!B:S,17,0)</f>
         <v>0</v>
       </c>
       <c r="T22" s="8">
-        <f>VLOOKUP(A22,'[1]19_DIAL100_RES'!B:H,6,0)</f>
+        <f>VLOOKUP(A22,'[1]21_NEWS360AI'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="U22" s="8">
-        <f>VLOOKUP(A22,'[1]20_CCTV_360'!B:S,17,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A22,'[1]22_eFSL'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="V22" s="8">
-        <f>VLOOKUP(A22,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <f>VLOOKUP(A22,'[1]23_UC3'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="W22" s="8">
-        <f>VLOOKUP(A22,'[1]22_eFSL'!B:F,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="X22" s="8">
-        <f>VLOOKUP(A22,'[1]23_UC3'!B:D,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y22" s="8">
         <f>VLOOKUP(A22,'[1]23_UC4'!B:D,3,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:25" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B23" s="8" t="str">
         <f>VLOOKUP(A23,'[1]1_MEDLEAPR_PME'!B:H,6,0)</f>
@@ -21551,65 +19904,56 @@
         <v>38.353413654618471</v>
       </c>
       <c r="L23" s="8">
-        <f>VLOOKUP(A23,'[1]11_e DAR'!B:F,4,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A23,'[1]12_CEIR'!B:L,10,0)</f>
+        <v>0</v>
       </c>
       <c r="M23" s="8">
-        <f>VLOOKUP(A23,'[1]12_CEIR'!B:L,10,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A23,'[1]13_EPROSEC'!B:H,4,0)</f>
+        <v>100</v>
       </c>
       <c r="N23" s="8">
-        <f>VLOOKUP(A23,'[1]13_EPROSEC'!B:H,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="O23" s="8">
         <f>VLOOKUP(A23,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
         <v>97.368421052631589</v>
       </c>
+      <c r="O23" s="8">
+        <f>VLOOKUP(A23,'[1]15_EOFFICE'!B:K,9,0)</f>
+        <v>0</v>
+      </c>
       <c r="P23" s="8">
-        <f>VLOOKUP(A23,'[1]15_EOFFICE'!B:K,9,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="8">
         <f>VLOOKUP(A23,'[1]16_APOLIS'!B:K,10,0)</f>
         <v>83.333333333333343</v>
       </c>
+      <c r="Q23" s="14">
+        <v>0</v>
+      </c>
       <c r="R23" s="8">
-        <f>VLOOKUP(A23,'[1]17_DRONE_FLYING'!B:J,9,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A23,'[1]11_e DAR'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="S23" s="8">
-        <f>VLOOKUP(A23,'[1]18_112_TABS'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T23" s="8">
-        <f>VLOOKUP(A23,'[1]19_DIAL100_RES'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U23" s="8">
         <f>VLOOKUP(A23,'[1]20_CCTV_360'!B:S,17,0)</f>
         <v>85.714285714285708</v>
       </c>
+      <c r="T23" s="8">
+        <f>VLOOKUP(A23,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U23" s="8">
+        <f>VLOOKUP(A23,'[1]22_eFSL'!B:F,4,0)</f>
+        <v>100</v>
+      </c>
       <c r="V23" s="8">
-        <f>VLOOKUP(A23,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <f>VLOOKUP(A23,'[1]23_UC3'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="W23" s="8">
-        <f>VLOOKUP(A23,'[1]22_eFSL'!B:F,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="X23" s="8">
-        <f>VLOOKUP(A23,'[1]23_UC3'!B:D,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y23" s="8">
         <f>VLOOKUP(A23,'[1]23_UC4'!B:D,3,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:25" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B24" s="8" t="str">
         <f>VLOOKUP(A24,'[1]1_MEDLEAPR_PME'!B:H,6,0)</f>
@@ -21652,65 +19996,56 @@
         <v>43.87096774193548</v>
       </c>
       <c r="L24" s="8">
-        <f>VLOOKUP(A24,'[1]11_e DAR'!B:F,4,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A24,'[1]12_CEIR'!B:L,10,0)</f>
+        <v>0</v>
       </c>
       <c r="M24" s="8">
-        <f>VLOOKUP(A24,'[1]12_CEIR'!B:L,10,0)</f>
-        <v>0</v>
-      </c>
-      <c r="N24" s="8">
         <f>VLOOKUP(A24,'[1]13_EPROSEC'!B:H,4,0)</f>
         <v>14.285714285714286</v>
       </c>
+      <c r="N24" s="8">
+        <f>VLOOKUP(A24,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
+        <v>100</v>
+      </c>
       <c r="O24" s="8">
-        <f>VLOOKUP(A24,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A24,'[1]15_EOFFICE'!B:K,9,0)</f>
+        <v>0</v>
       </c>
       <c r="P24" s="8">
-        <f>VLOOKUP(A24,'[1]15_EOFFICE'!B:K,9,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q24" s="8">
         <f>VLOOKUP(A24,'[1]16_APOLIS'!B:K,10,0)</f>
         <v>83.333333333333343</v>
       </c>
+      <c r="Q24" s="14">
+        <v>0</v>
+      </c>
       <c r="R24" s="8">
-        <f>VLOOKUP(A24,'[1]17_DRONE_FLYING'!B:J,9,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A24,'[1]11_e DAR'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="S24" s="8">
-        <f>VLOOKUP(A24,'[1]18_112_TABS'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T24" s="8">
-        <f>VLOOKUP(A24,'[1]19_DIAL100_RES'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U24" s="8">
         <f>VLOOKUP(A24,'[1]20_CCTV_360'!B:S,17,0)</f>
         <v>64.285714285714292</v>
       </c>
+      <c r="T24" s="8">
+        <f>VLOOKUP(A24,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U24" s="8">
+        <f>VLOOKUP(A24,'[1]22_eFSL'!B:F,4,0)</f>
+        <v>100</v>
+      </c>
       <c r="V24" s="8">
-        <f>VLOOKUP(A24,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <f>VLOOKUP(A24,'[1]23_UC3'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="W24" s="8">
-        <f>VLOOKUP(A24,'[1]22_eFSL'!B:F,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="X24" s="8">
-        <f>VLOOKUP(A24,'[1]23_UC3'!B:D,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y24" s="8">
         <f>VLOOKUP(A24,'[1]23_UC4'!B:D,3,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:25" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B25" s="8">
         <f>VLOOKUP(A25,'[1]1_MEDLEAPR_PME'!B:H,6,0)</f>
@@ -21753,65 +20088,56 @@
         <v>38.047559449311642</v>
       </c>
       <c r="L25" s="8">
-        <f>VLOOKUP(A25,'[1]11_e DAR'!B:F,4,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A25,'[1]12_CEIR'!B:L,10,0)</f>
+        <v>0</v>
       </c>
       <c r="M25" s="8">
-        <f>VLOOKUP(A25,'[1]12_CEIR'!B:L,10,0)</f>
-        <v>0</v>
-      </c>
-      <c r="N25" s="8">
         <f>VLOOKUP(A25,'[1]13_EPROSEC'!B:H,4,0)</f>
         <v>14.285714285714286</v>
       </c>
-      <c r="O25" s="8">
+      <c r="N25" s="8">
         <f>VLOOKUP(A25,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
         <v>47.234104046242777</v>
       </c>
+      <c r="O25" s="8">
+        <f>VLOOKUP(A25,'[1]15_EOFFICE'!B:K,9,0)</f>
+        <v>0</v>
+      </c>
       <c r="P25" s="8">
-        <f>VLOOKUP(A25,'[1]15_EOFFICE'!B:K,9,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q25" s="8">
         <f>VLOOKUP(A25,'[1]16_APOLIS'!B:K,10,0)</f>
         <v>93.243243243243242</v>
       </c>
+      <c r="Q25" s="14">
+        <v>0</v>
+      </c>
       <c r="R25" s="8">
-        <f>VLOOKUP(A25,'[1]17_DRONE_FLYING'!B:J,9,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A25,'[1]11_e DAR'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="S25" s="8">
-        <f>VLOOKUP(A25,'[1]18_112_TABS'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T25" s="8">
-        <f>VLOOKUP(A25,'[1]19_DIAL100_RES'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U25" s="8">
         <f>VLOOKUP(A25,'[1]20_CCTV_360'!B:S,17,0)</f>
         <v>64.285714285714292</v>
       </c>
+      <c r="T25" s="8">
+        <f>VLOOKUP(A25,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U25" s="8">
+        <f>VLOOKUP(A25,'[1]22_eFSL'!B:F,4,0)</f>
+        <v>100</v>
+      </c>
       <c r="V25" s="8">
-        <f>VLOOKUP(A25,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <f>VLOOKUP(A25,'[1]23_UC3'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="W25" s="8">
-        <f>VLOOKUP(A25,'[1]22_eFSL'!B:F,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="X25" s="8">
-        <f>VLOOKUP(A25,'[1]23_UC3'!B:D,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y25" s="8">
         <f>VLOOKUP(A25,'[1]23_UC4'!B:D,3,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:25" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B26" s="8">
         <f>VLOOKUP(A26,'[1]1_MEDLEAPR_PME'!B:H,6,0)</f>
@@ -21854,65 +20180,56 @@
         <v>80.131578947368425</v>
       </c>
       <c r="L26" s="8">
-        <f>VLOOKUP(A26,'[1]11_e DAR'!B:F,4,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A26,'[1]12_CEIR'!B:L,10,0)</f>
+        <v>0</v>
       </c>
       <c r="M26" s="8">
-        <f>VLOOKUP(A26,'[1]12_CEIR'!B:L,10,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A26,'[1]13_EPROSEC'!B:H,4,0)</f>
+        <v>100</v>
       </c>
       <c r="N26" s="8">
-        <f>VLOOKUP(A26,'[1]13_EPROSEC'!B:H,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="O26" s="8">
         <f>VLOOKUP(A26,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
         <v>96.794871794871796</v>
       </c>
+      <c r="O26" s="8">
+        <f>VLOOKUP(A26,'[1]15_EOFFICE'!B:K,9,0)</f>
+        <v>0</v>
+      </c>
       <c r="P26" s="8">
-        <f>VLOOKUP(A26,'[1]15_EOFFICE'!B:K,9,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="8">
         <f>VLOOKUP(A26,'[1]16_APOLIS'!B:K,10,0)</f>
         <v>85.294117647058826</v>
       </c>
+      <c r="Q26" s="14">
+        <v>0</v>
+      </c>
       <c r="R26" s="8">
-        <f>VLOOKUP(A26,'[1]17_DRONE_FLYING'!B:J,9,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A26,'[1]11_e DAR'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="S26" s="8">
-        <f>VLOOKUP(A26,'[1]18_112_TABS'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T26" s="8">
-        <f>VLOOKUP(A26,'[1]19_DIAL100_RES'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U26" s="8">
         <f>VLOOKUP(A26,'[1]20_CCTV_360'!B:S,17,0)</f>
         <v>85.714285714285708</v>
       </c>
+      <c r="T26" s="8">
+        <f>VLOOKUP(A26,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U26" s="8">
+        <f>VLOOKUP(A26,'[1]22_eFSL'!B:F,4,0)</f>
+        <v>0</v>
+      </c>
       <c r="V26" s="8">
-        <f>VLOOKUP(A26,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <f>VLOOKUP(A26,'[1]23_UC3'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="W26" s="8">
-        <f>VLOOKUP(A26,'[1]22_eFSL'!B:F,4,0)</f>
-        <v>0</v>
-      </c>
-      <c r="X26" s="8">
-        <f>VLOOKUP(A26,'[1]23_UC3'!B:D,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y26" s="8">
         <f>VLOOKUP(A26,'[1]23_UC4'!B:D,3,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:25" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B27" s="8" t="str">
         <f>VLOOKUP(A27,'[1]1_MEDLEAPR_PME'!B:H,6,0)</f>
@@ -21955,65 +20272,56 @@
         <v>55.860349127182047</v>
       </c>
       <c r="L27" s="8">
-        <f>VLOOKUP(A27,'[1]11_e DAR'!B:F,4,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A27,'[1]12_CEIR'!B:L,10,0)</f>
+        <v>0</v>
       </c>
       <c r="M27" s="8">
-        <f>VLOOKUP(A27,'[1]12_CEIR'!B:L,10,0)</f>
-        <v>0</v>
-      </c>
-      <c r="N27" s="8">
         <f>VLOOKUP(A27,'[1]13_EPROSEC'!B:H,4,0)</f>
         <v>25</v>
       </c>
-      <c r="O27" s="8">
+      <c r="N27" s="8">
         <f>VLOOKUP(A27,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
         <v>98.245614035087726</v>
       </c>
+      <c r="O27" s="8">
+        <f>VLOOKUP(A27,'[1]15_EOFFICE'!B:K,9,0)</f>
+        <v>0</v>
+      </c>
       <c r="P27" s="8">
-        <f>VLOOKUP(A27,'[1]15_EOFFICE'!B:K,9,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q27" s="8">
         <f>VLOOKUP(A27,'[1]16_APOLIS'!B:K,10,0)</f>
         <v>82.142857142857139</v>
       </c>
+      <c r="Q27" s="14">
+        <v>0</v>
+      </c>
       <c r="R27" s="8">
-        <f>VLOOKUP(A27,'[1]17_DRONE_FLYING'!B:J,9,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A27,'[1]11_e DAR'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="S27" s="8">
-        <f>VLOOKUP(A27,'[1]18_112_TABS'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T27" s="8">
-        <f>VLOOKUP(A27,'[1]19_DIAL100_RES'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U27" s="8">
         <f>VLOOKUP(A27,'[1]20_CCTV_360'!B:S,17,0)</f>
         <v>14.285714285714285</v>
       </c>
+      <c r="T27" s="8">
+        <f>VLOOKUP(A27,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U27" s="8">
+        <f>VLOOKUP(A27,'[1]22_eFSL'!B:F,4,0)</f>
+        <v>0</v>
+      </c>
       <c r="V27" s="8">
-        <f>VLOOKUP(A27,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <f>VLOOKUP(A27,'[1]23_UC3'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="W27" s="8">
-        <f>VLOOKUP(A27,'[1]22_eFSL'!B:F,4,0)</f>
-        <v>0</v>
-      </c>
-      <c r="X27" s="8">
-        <f>VLOOKUP(A27,'[1]23_UC3'!B:D,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y27" s="8">
         <f>VLOOKUP(A27,'[1]23_UC4'!B:D,3,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:25" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B28" s="8" t="str">
         <f>VLOOKUP(A28,'[1]1_MEDLEAPR_PME'!B:H,6,0)</f>
@@ -22056,65 +20364,56 @@
         <v>93.11926605504587</v>
       </c>
       <c r="L28" s="8">
-        <f>VLOOKUP(A28,'[1]11_e DAR'!B:F,4,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A28,'[1]12_CEIR'!B:L,10,0)</f>
+        <v>0</v>
       </c>
       <c r="M28" s="8">
-        <f>VLOOKUP(A28,'[1]12_CEIR'!B:L,10,0)</f>
+        <f>VLOOKUP(A28,'[1]13_EPROSEC'!B:H,4,0)</f>
         <v>0</v>
       </c>
       <c r="N28" s="8">
-        <f>VLOOKUP(A28,'[1]13_EPROSEC'!B:H,4,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A28,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
+        <v>100</v>
       </c>
       <c r="O28" s="8">
-        <f>VLOOKUP(A28,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A28,'[1]15_EOFFICE'!B:K,9,0)</f>
+        <v>0</v>
       </c>
       <c r="P28" s="8">
-        <f>VLOOKUP(A28,'[1]15_EOFFICE'!B:K,9,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q28" s="8">
         <f>VLOOKUP(A28,'[1]16_APOLIS'!B:K,10,0)</f>
         <v>83.333333333333343</v>
       </c>
+      <c r="Q28" s="14">
+        <v>0</v>
+      </c>
       <c r="R28" s="8">
-        <f>VLOOKUP(A28,'[1]17_DRONE_FLYING'!B:J,9,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A28,'[1]11_e DAR'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="S28" s="8">
-        <f>VLOOKUP(A28,'[1]18_112_TABS'!B:H,6,0)</f>
+        <f>VLOOKUP(A28,'[1]20_CCTV_360'!B:S,17,0)</f>
         <v>0</v>
       </c>
       <c r="T28" s="8">
-        <f>VLOOKUP(A28,'[1]19_DIAL100_RES'!B:H,6,0)</f>
+        <f>VLOOKUP(A28,'[1]21_NEWS360AI'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="U28" s="8">
-        <f>VLOOKUP(A28,'[1]20_CCTV_360'!B:S,17,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A28,'[1]22_eFSL'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="V28" s="8">
-        <f>VLOOKUP(A28,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <f>VLOOKUP(A28,'[1]23_UC3'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="W28" s="8">
-        <f>VLOOKUP(A28,'[1]22_eFSL'!B:F,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="X28" s="8">
-        <f>VLOOKUP(A28,'[1]23_UC3'!B:D,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y28" s="8">
         <f>VLOOKUP(A28,'[1]23_UC4'!B:D,3,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:25" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B29" s="8" t="str">
         <f>VLOOKUP(A29,'[1]1_MEDLEAPR_PME'!B:H,6,0)</f>
@@ -22157,65 +20456,56 @@
         <v>43.96551724137931</v>
       </c>
       <c r="L29" s="8">
-        <f>VLOOKUP(A29,'[1]11_e DAR'!B:F,4,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A29,'[1]12_CEIR'!B:L,10,0)</f>
+        <v>0</v>
       </c>
       <c r="M29" s="8">
-        <f>VLOOKUP(A29,'[1]12_CEIR'!B:L,10,0)</f>
-        <v>0</v>
-      </c>
-      <c r="N29" s="8">
         <f>VLOOKUP(A29,'[1]13_EPROSEC'!B:H,4,0)</f>
         <v>25</v>
       </c>
+      <c r="N29" s="8">
+        <f>VLOOKUP(A29,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
+        <v>100</v>
+      </c>
       <c r="O29" s="8">
-        <f>VLOOKUP(A29,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A29,'[1]15_EOFFICE'!B:K,9,0)</f>
+        <v>0</v>
       </c>
       <c r="P29" s="8">
-        <f>VLOOKUP(A29,'[1]15_EOFFICE'!B:K,9,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q29" s="8">
         <f>VLOOKUP(A29,'[1]16_APOLIS'!B:K,10,0)</f>
         <v>83.333333333333343</v>
       </c>
+      <c r="Q29" s="14">
+        <v>0</v>
+      </c>
       <c r="R29" s="8">
-        <f>VLOOKUP(A29,'[1]17_DRONE_FLYING'!B:J,9,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A29,'[1]11_e DAR'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="S29" s="8">
-        <f>VLOOKUP(A29,'[1]18_112_TABS'!B:H,6,0)</f>
+        <f>VLOOKUP(A29,'[1]20_CCTV_360'!B:S,17,0)</f>
         <v>0</v>
       </c>
       <c r="T29" s="8">
-        <f>VLOOKUP(A29,'[1]19_DIAL100_RES'!B:H,6,0)</f>
+        <f>VLOOKUP(A29,'[1]21_NEWS360AI'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="U29" s="8">
-        <f>VLOOKUP(A29,'[1]20_CCTV_360'!B:S,17,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A29,'[1]22_eFSL'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="V29" s="8">
-        <f>VLOOKUP(A29,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <f>VLOOKUP(A29,'[1]23_UC3'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="W29" s="8">
-        <f>VLOOKUP(A29,'[1]22_eFSL'!B:F,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="X29" s="8">
-        <f>VLOOKUP(A29,'[1]23_UC3'!B:D,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y29" s="8">
         <f>VLOOKUP(A29,'[1]23_UC4'!B:D,3,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:25" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B30" s="8" t="str">
         <f>VLOOKUP(A30,'[1]1_MEDLEAPR_PME'!B:H,6,0)</f>
@@ -22258,65 +20548,56 @@
         <v>72.376873661670231</v>
       </c>
       <c r="L30" s="8">
-        <f>VLOOKUP(A30,'[1]11_e DAR'!B:F,4,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A30,'[1]12_CEIR'!B:L,10,0)</f>
+        <v>0</v>
       </c>
       <c r="M30" s="8">
-        <f>VLOOKUP(A30,'[1]12_CEIR'!B:L,10,0)</f>
-        <v>0</v>
-      </c>
-      <c r="N30" s="8">
         <f>VLOOKUP(A30,'[1]13_EPROSEC'!B:H,4,0)</f>
         <v>25</v>
       </c>
-      <c r="O30" s="8">
+      <c r="N30" s="8">
         <f>VLOOKUP(A30,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
         <v>98.75</v>
       </c>
+      <c r="O30" s="8">
+        <f>VLOOKUP(A30,'[1]15_EOFFICE'!B:K,9,0)</f>
+        <v>0</v>
+      </c>
       <c r="P30" s="8">
-        <f>VLOOKUP(A30,'[1]15_EOFFICE'!B:K,9,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q30" s="8">
         <f>VLOOKUP(A30,'[1]16_APOLIS'!B:K,10,0)</f>
         <v>83.333333333333343</v>
       </c>
+      <c r="Q30" s="14">
+        <v>0</v>
+      </c>
       <c r="R30" s="8">
-        <f>VLOOKUP(A30,'[1]17_DRONE_FLYING'!B:J,9,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A30,'[1]11_e DAR'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="S30" s="8">
-        <f>VLOOKUP(A30,'[1]18_112_TABS'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T30" s="8">
-        <f>VLOOKUP(A30,'[1]19_DIAL100_RES'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U30" s="8">
         <f>VLOOKUP(A30,'[1]20_CCTV_360'!B:S,17,0)</f>
         <v>50</v>
       </c>
+      <c r="T30" s="8">
+        <f>VLOOKUP(A30,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U30" s="8">
+        <f>VLOOKUP(A30,'[1]22_eFSL'!B:F,4,0)</f>
+        <v>100</v>
+      </c>
       <c r="V30" s="8">
-        <f>VLOOKUP(A30,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <f>VLOOKUP(A30,'[1]23_UC3'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="W30" s="8">
-        <f>VLOOKUP(A30,'[1]22_eFSL'!B:F,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="X30" s="8">
-        <f>VLOOKUP(A30,'[1]23_UC3'!B:D,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y30" s="8">
         <f>VLOOKUP(A30,'[1]23_UC4'!B:D,3,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:25" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B31" s="8" t="str">
         <f>VLOOKUP(A31,'[1]1_MEDLEAPR_PME'!B:H,6,0)</f>
@@ -22359,65 +20640,56 @@
         <v>44.090056285178235</v>
       </c>
       <c r="L31" s="8">
-        <f>VLOOKUP(A31,'[1]11_e DAR'!B:F,4,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A31,'[1]12_CEIR'!B:L,10,0)</f>
+        <v>0</v>
       </c>
       <c r="M31" s="8">
-        <f>VLOOKUP(A31,'[1]12_CEIR'!B:L,10,0)</f>
-        <v>0</v>
-      </c>
-      <c r="N31" s="8">
         <f>VLOOKUP(A31,'[1]13_EPROSEC'!B:H,4,0)</f>
         <v>20</v>
       </c>
-      <c r="O31" s="8">
+      <c r="N31" s="8">
         <f>VLOOKUP(A31,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
         <v>50.644438217988231</v>
       </c>
+      <c r="O31" s="8">
+        <f>VLOOKUP(A31,'[1]15_EOFFICE'!B:K,9,0)</f>
+        <v>0</v>
+      </c>
       <c r="P31" s="8">
-        <f>VLOOKUP(A31,'[1]15_EOFFICE'!B:K,9,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q31" s="8">
         <f>VLOOKUP(A31,'[1]16_APOLIS'!B:K,10,0)</f>
         <v>83.928571428571431</v>
       </c>
+      <c r="Q31" s="14">
+        <v>0</v>
+      </c>
       <c r="R31" s="8">
-        <f>VLOOKUP(A31,'[1]17_DRONE_FLYING'!B:J,9,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A31,'[1]11_e DAR'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="S31" s="8">
-        <f>VLOOKUP(A31,'[1]18_112_TABS'!B:H,6,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A31,'[1]20_CCTV_360'!B:S,17,0)</f>
+        <v>100</v>
       </c>
       <c r="T31" s="8">
-        <f>VLOOKUP(A31,'[1]19_DIAL100_RES'!B:H,6,0)</f>
+        <f>VLOOKUP(A31,'[1]21_NEWS360AI'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="U31" s="8">
-        <f>VLOOKUP(A31,'[1]20_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A31,'[1]22_eFSL'!B:F,4,0)</f>
         <v>100</v>
       </c>
       <c r="V31" s="8">
-        <f>VLOOKUP(A31,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <f>VLOOKUP(A31,'[1]23_UC3'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="W31" s="8">
-        <f>VLOOKUP(A31,'[1]22_eFSL'!B:F,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="X31" s="8">
-        <f>VLOOKUP(A31,'[1]23_UC3'!B:D,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y31" s="8">
         <f>VLOOKUP(A31,'[1]23_UC4'!B:D,3,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:25" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B32" s="8" t="str">
         <f>VLOOKUP(A32,'[1]1_MEDLEAPR_PME'!B:H,6,0)</f>
@@ -22460,65 +20732,56 @@
         <v>92.901234567901241</v>
       </c>
       <c r="L32" s="8">
-        <f>VLOOKUP(A32,'[1]11_e DAR'!B:F,4,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A32,'[1]12_CEIR'!B:L,10,0)</f>
+        <v>0</v>
       </c>
       <c r="M32" s="8">
-        <f>VLOOKUP(A32,'[1]12_CEIR'!B:L,10,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A32,'[1]13_EPROSEC'!B:H,4,0)</f>
+        <v>100</v>
       </c>
       <c r="N32" s="8">
-        <f>VLOOKUP(A32,'[1]13_EPROSEC'!B:H,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="O32" s="8">
         <f>VLOOKUP(A32,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
         <v>94.73684210526315</v>
       </c>
+      <c r="O32" s="8">
+        <f>VLOOKUP(A32,'[1]15_EOFFICE'!B:K,9,0)</f>
+        <v>0</v>
+      </c>
       <c r="P32" s="8">
-        <f>VLOOKUP(A32,'[1]15_EOFFICE'!B:K,9,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q32" s="8">
         <f>VLOOKUP(A32,'[1]16_APOLIS'!B:K,10,0)</f>
         <v>82.142857142857139</v>
       </c>
+      <c r="Q32" s="14">
+        <v>0</v>
+      </c>
       <c r="R32" s="8">
-        <f>VLOOKUP(A32,'[1]17_DRONE_FLYING'!B:J,9,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A32,'[1]11_e DAR'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="S32" s="8">
-        <f>VLOOKUP(A32,'[1]18_112_TABS'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T32" s="8">
-        <f>VLOOKUP(A32,'[1]19_DIAL100_RES'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U32" s="8">
         <f>VLOOKUP(A32,'[1]20_CCTV_360'!B:S,17,0)</f>
         <v>28.571428571428569</v>
       </c>
+      <c r="T32" s="8">
+        <f>VLOOKUP(A32,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U32" s="8">
+        <f>VLOOKUP(A32,'[1]22_eFSL'!B:F,4,0)</f>
+        <v>100</v>
+      </c>
       <c r="V32" s="8">
-        <f>VLOOKUP(A32,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <f>VLOOKUP(A32,'[1]23_UC3'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="W32" s="8">
-        <f>VLOOKUP(A32,'[1]22_eFSL'!B:F,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="X32" s="8">
-        <f>VLOOKUP(A32,'[1]23_UC3'!B:D,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y32" s="8">
         <f>VLOOKUP(A32,'[1]23_UC4'!B:D,3,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:25" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B33" s="8">
         <f>VLOOKUP(A33,'[1]1_MEDLEAPR_PME'!B:H,6,0)</f>
@@ -22561,65 +20824,56 @@
         <v>94.690265486725664</v>
       </c>
       <c r="L33" s="8">
-        <f>VLOOKUP(A33,'[1]11_e DAR'!B:F,4,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A33,'[1]12_CEIR'!B:L,10,0)</f>
+        <v>0</v>
       </c>
       <c r="M33" s="8">
-        <f>VLOOKUP(A33,'[1]12_CEIR'!B:L,10,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A33,'[1]13_EPROSEC'!B:H,4,0)</f>
+        <v>100</v>
       </c>
       <c r="N33" s="8">
-        <f>VLOOKUP(A33,'[1]13_EPROSEC'!B:H,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="O33" s="8">
         <f>VLOOKUP(A33,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
         <v>96.341463414634148</v>
       </c>
+      <c r="O33" s="8">
+        <f>VLOOKUP(A33,'[1]15_EOFFICE'!B:K,9,0)</f>
+        <v>0</v>
+      </c>
       <c r="P33" s="8">
-        <f>VLOOKUP(A33,'[1]15_EOFFICE'!B:K,9,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q33" s="8">
         <f>VLOOKUP(A33,'[1]16_APOLIS'!B:K,10,0)</f>
         <v>85</v>
       </c>
+      <c r="Q33" s="14">
+        <v>0</v>
+      </c>
       <c r="R33" s="8">
-        <f>VLOOKUP(A33,'[1]17_DRONE_FLYING'!B:J,9,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A33,'[1]11_e DAR'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="S33" s="8">
-        <f>VLOOKUP(A33,'[1]18_112_TABS'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T33" s="8">
-        <f>VLOOKUP(A33,'[1]19_DIAL100_RES'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U33" s="8">
         <f>VLOOKUP(A33,'[1]20_CCTV_360'!B:S,17,0)</f>
         <v>78.571428571428569</v>
       </c>
+      <c r="T33" s="8">
+        <f>VLOOKUP(A33,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U33" s="8">
+        <f>VLOOKUP(A33,'[1]22_eFSL'!B:F,4,0)</f>
+        <v>100</v>
+      </c>
       <c r="V33" s="8">
-        <f>VLOOKUP(A33,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <f>VLOOKUP(A33,'[1]23_UC3'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="W33" s="8">
-        <f>VLOOKUP(A33,'[1]22_eFSL'!B:F,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="X33" s="8">
-        <f>VLOOKUP(A33,'[1]23_UC3'!B:D,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y33" s="8">
         <f>VLOOKUP(A33,'[1]23_UC4'!B:D,3,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:25" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B34" s="8">
         <f>VLOOKUP(A34,'[1]1_MEDLEAPR_PME'!B:H,6,0)</f>
@@ -22662,65 +20916,56 @@
         <v>81.496062992125985</v>
       </c>
       <c r="L34" s="8">
-        <f>VLOOKUP(A34,'[1]11_e DAR'!B:F,4,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A34,'[1]12_CEIR'!B:L,10,0)</f>
+        <v>0</v>
       </c>
       <c r="M34" s="8">
-        <f>VLOOKUP(A34,'[1]12_CEIR'!B:L,10,0)</f>
+        <f>VLOOKUP(A34,'[1]13_EPROSEC'!B:H,4,0)</f>
         <v>0</v>
       </c>
       <c r="N34" s="8">
-        <f>VLOOKUP(A34,'[1]13_EPROSEC'!B:H,4,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A34,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
+        <v>100</v>
       </c>
       <c r="O34" s="8">
-        <f>VLOOKUP(A34,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A34,'[1]15_EOFFICE'!B:K,9,0)</f>
+        <v>0</v>
       </c>
       <c r="P34" s="8">
-        <f>VLOOKUP(A34,'[1]15_EOFFICE'!B:K,9,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q34" s="8">
         <f>VLOOKUP(A34,'[1]16_APOLIS'!B:K,10,0)</f>
         <v>85</v>
       </c>
+      <c r="Q34" s="14">
+        <v>0</v>
+      </c>
       <c r="R34" s="8">
-        <f>VLOOKUP(A34,'[1]17_DRONE_FLYING'!B:J,9,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A34,'[1]11_e DAR'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="S34" s="8">
-        <f>VLOOKUP(A34,'[1]18_112_TABS'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T34" s="8">
-        <f>VLOOKUP(A34,'[1]19_DIAL100_RES'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U34" s="8">
         <f>VLOOKUP(A34,'[1]20_CCTV_360'!B:S,17,0)</f>
         <v>71.428571428571431</v>
       </c>
+      <c r="T34" s="8">
+        <f>VLOOKUP(A34,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U34" s="8">
+        <f>VLOOKUP(A34,'[1]22_eFSL'!B:F,4,0)</f>
+        <v>100</v>
+      </c>
       <c r="V34" s="8">
-        <f>VLOOKUP(A34,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <f>VLOOKUP(A34,'[1]23_UC3'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="W34" s="8">
-        <f>VLOOKUP(A34,'[1]22_eFSL'!B:F,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="X34" s="8">
-        <f>VLOOKUP(A34,'[1]23_UC3'!B:D,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y34" s="8">
         <f>VLOOKUP(A34,'[1]23_UC4'!B:D,3,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:25" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B35" s="8" t="str">
         <f>VLOOKUP(A35,'[1]1_MEDLEAPR_PME'!B:H,6,0)</f>
@@ -22763,58 +21008,49 @@
         <v>82.608695652173907</v>
       </c>
       <c r="L35" s="8">
-        <f>VLOOKUP(A35,'[1]11_e DAR'!B:F,4,0)</f>
-        <v>100</v>
+        <f>VLOOKUP(A35,'[1]12_CEIR'!B:L,10,0)</f>
+        <v>0</v>
       </c>
       <c r="M35" s="8">
-        <f>VLOOKUP(A35,'[1]12_CEIR'!B:L,10,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A35,'[1]13_EPROSEC'!B:H,4,0)</f>
+        <v>100</v>
       </c>
       <c r="N35" s="8">
-        <f>VLOOKUP(A35,'[1]13_EPROSEC'!B:H,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="O35" s="8">
         <f>VLOOKUP(A35,'[1]14_FIR_CS_COURT'!B:L,11,0)</f>
         <v>50</v>
       </c>
+      <c r="O35" s="8">
+        <f>VLOOKUP(A35,'[1]15_EOFFICE'!B:K,9,0)</f>
+        <v>0</v>
+      </c>
       <c r="P35" s="8">
-        <f>VLOOKUP(A35,'[1]15_EOFFICE'!B:K,9,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q35" s="8">
         <f>VLOOKUP(A35,'[1]16_APOLIS'!B:K,10,0)</f>
         <v>87.5</v>
       </c>
+      <c r="Q35" s="14">
+        <v>0</v>
+      </c>
       <c r="R35" s="8">
-        <f>VLOOKUP(A35,'[1]17_DRONE_FLYING'!B:J,9,0)</f>
-        <v>0</v>
+        <f>VLOOKUP(A35,'[1]11_e DAR'!B:F,4,0)</f>
+        <v>100</v>
       </c>
       <c r="S35" s="8">
-        <f>VLOOKUP(A35,'[1]18_112_TABS'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T35" s="8">
-        <f>VLOOKUP(A35,'[1]19_DIAL100_RES'!B:H,6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U35" s="8">
         <f>VLOOKUP(A35,'[1]20_CCTV_360'!B:S,17,0)</f>
         <v>71.428571428571431</v>
       </c>
+      <c r="T35" s="8">
+        <f>VLOOKUP(A35,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U35" s="8">
+        <f>VLOOKUP(A35,'[1]22_eFSL'!B:F,4,0)</f>
+        <v>100</v>
+      </c>
       <c r="V35" s="8">
-        <f>VLOOKUP(A35,'[1]21_NEWS360AI'!B:D,2,0)</f>
+        <f>VLOOKUP(A35,'[1]23_UC3'!B:D,2,0)</f>
         <v>0</v>
       </c>
       <c r="W35" s="8">
-        <f>VLOOKUP(A35,'[1]22_eFSL'!B:F,4,0)</f>
-        <v>100</v>
-      </c>
-      <c r="X35" s="8">
-        <f>VLOOKUP(A35,'[1]23_UC3'!B:D,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y35" s="8">
         <f>VLOOKUP(A35,'[1]23_UC4'!B:D,3,0)</f>
         <v>0</v>
       </c>
@@ -22823,4 +21059,85 @@
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="91" fitToHeight="0" orientation="landscape" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E76EFDEE-BD64-4E0D-98CC-CC3107D8DC4D}">
+  <dimension ref="A1:Y1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:25" s="13" customFormat="1" ht="47.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="4"/>
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="O1" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="P1" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q1" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="R1" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="S1" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" s="5"/>
+      <c r="Y1" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/weeks/AKP_PS_16_09_2026-24_09_2026.xlsx
+++ b/data/weeks/AKP_PS_16_09_2026-24_09_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026 Data\AKP Smart Policing Data\WEB UPLOADS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kolak\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B81CD9BB-FD01-470E-910A-51B90E5EA1B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A4ED5D6-0692-47BF-8601-E4533B422895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A070338D-36A4-404F-A675-F337B1AAFE60}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BC89355F-0941-4B6D-8CC1-D4FB4457EF93}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -403,8 +403,8 @@
       <sheetName val="14_EOFFICE"/>
       <sheetName val="15_APOLIS"/>
       <sheetName val="16_APOLICE_FP"/>
-      <sheetName val="17_EDAR"/>
-      <sheetName val="18_CCTV_360"/>
+      <sheetName val="17_CCTV_360"/>
+      <sheetName val="18_EDAR"/>
       <sheetName val="19_NEWS360AI"/>
       <sheetName val="20_eFSL"/>
       <sheetName val="21_UC3"/>
@@ -15017,274 +15017,648 @@
       <sheetData sheetId="16">
         <row r="2">
           <cell r="B2" t="str">
-            <v>PS Name</v>
-          </cell>
-          <cell r="C2" t="str">
-            <v xml:space="preserve">Total FIRS 
-Registered </v>
-          </cell>
-          <cell r="D2" t="str">
-            <v>Total FORM1 Uploads</v>
-          </cell>
-          <cell r="E2" t="str">
-            <v>Raw Value</v>
-          </cell>
-          <cell r="F2" t="str">
-            <v>Marks</v>
+            <v>PS</v>
+          </cell>
+          <cell r="C2">
+            <v>46281</v>
+          </cell>
+          <cell r="E2">
+            <v>46281</v>
+          </cell>
+          <cell r="G2">
+            <v>2</v>
+          </cell>
+          <cell r="I2">
+            <v>3</v>
+          </cell>
+          <cell r="K2">
+            <v>4</v>
+          </cell>
+          <cell r="M2">
+            <v>5</v>
+          </cell>
+          <cell r="O2">
+            <v>6</v>
+          </cell>
+          <cell r="Q2" t="str">
+            <v>MARKS</v>
+          </cell>
+          <cell r="R2" t="str">
+            <v>RAW VALUE</v>
           </cell>
         </row>
         <row r="3">
-          <cell r="B3" t="str">
-            <v>A.Koduru</v>
-          </cell>
-          <cell r="E3">
-            <v>100</v>
-          </cell>
-          <cell r="F3">
-            <v>10</v>
+          <cell r="C3" t="str">
+            <v>WEB</v>
+          </cell>
+          <cell r="D3" t="str">
+            <v>MOBILE</v>
+          </cell>
+          <cell r="E3" t="str">
+            <v>WEB</v>
+          </cell>
+          <cell r="F3" t="str">
+            <v>MOBILE</v>
+          </cell>
+          <cell r="G3" t="str">
+            <v>WEB</v>
+          </cell>
+          <cell r="H3" t="str">
+            <v>MOBILE</v>
+          </cell>
+          <cell r="I3" t="str">
+            <v>WEB</v>
+          </cell>
+          <cell r="J3" t="str">
+            <v>MOBILE</v>
+          </cell>
+          <cell r="K3" t="str">
+            <v>WEB</v>
+          </cell>
+          <cell r="L3" t="str">
+            <v>MOBILE</v>
+          </cell>
+          <cell r="M3" t="str">
+            <v>WEB</v>
+          </cell>
+          <cell r="N3" t="str">
+            <v>MOBILE</v>
+          </cell>
+          <cell r="O3" t="str">
+            <v>WEB</v>
+          </cell>
+          <cell r="P3" t="str">
+            <v>MOBILE</v>
           </cell>
         </row>
         <row r="4">
           <cell r="B4" t="str">
-            <v>Anakapalli Rural</v>
+            <v>A.Koduru</v>
+          </cell>
+          <cell r="C4">
+            <v>1</v>
           </cell>
           <cell r="E4">
-            <v>100</v>
+            <v>1</v>
           </cell>
           <cell r="F4">
-            <v>10</v>
+            <v>1</v>
+          </cell>
+          <cell r="H4">
+            <v>1</v>
+          </cell>
+          <cell r="I4">
+            <v>1</v>
+          </cell>
+          <cell r="J4">
+            <v>1</v>
+          </cell>
+          <cell r="K4">
+            <v>1</v>
+          </cell>
+          <cell r="M4">
+            <v>1</v>
+          </cell>
+          <cell r="N4">
+            <v>1</v>
+          </cell>
+          <cell r="O4">
+            <v>1</v>
+          </cell>
+          <cell r="Q4">
+            <v>3.5714285714285716</v>
+          </cell>
+          <cell r="R4">
+            <v>71.428571428571431</v>
           </cell>
         </row>
         <row r="5">
           <cell r="B5" t="str">
-            <v>Anakapalli Town</v>
+            <v>Anakapalli Rural</v>
+          </cell>
+          <cell r="C5">
+            <v>4</v>
+          </cell>
+          <cell r="D5">
+            <v>1</v>
           </cell>
           <cell r="E5">
-            <v>100</v>
+            <v>1</v>
           </cell>
           <cell r="F5">
-            <v>10</v>
+            <v>1</v>
+          </cell>
+          <cell r="G5">
+            <v>1</v>
+          </cell>
+          <cell r="H5">
+            <v>1</v>
+          </cell>
+          <cell r="I5">
+            <v>1</v>
+          </cell>
+          <cell r="J5">
+            <v>1</v>
+          </cell>
+          <cell r="K5">
+            <v>1</v>
+          </cell>
+          <cell r="L5">
+            <v>1</v>
+          </cell>
+          <cell r="M5">
+            <v>5</v>
+          </cell>
+          <cell r="N5">
+            <v>1</v>
+          </cell>
+          <cell r="O5">
+            <v>1</v>
+          </cell>
+          <cell r="Q5">
+            <v>4.6428571428571432</v>
+          </cell>
+          <cell r="R5">
+            <v>92.857142857142861</v>
           </cell>
         </row>
         <row r="6">
           <cell r="B6" t="str">
-            <v>Anakapalli Traffic</v>
+            <v>Anakapalli Town</v>
+          </cell>
+          <cell r="C6">
+            <v>2</v>
+          </cell>
+          <cell r="D6">
+            <v>1</v>
           </cell>
           <cell r="E6">
-            <v>100</v>
+            <v>2</v>
           </cell>
           <cell r="F6">
-            <v>10</v>
+            <v>1</v>
+          </cell>
+          <cell r="G6">
+            <v>1</v>
+          </cell>
+          <cell r="H6">
+            <v>1</v>
+          </cell>
+          <cell r="I6">
+            <v>2</v>
+          </cell>
+          <cell r="J6">
+            <v>1</v>
+          </cell>
+          <cell r="K6">
+            <v>1</v>
+          </cell>
+          <cell r="L6">
+            <v>1</v>
+          </cell>
+          <cell r="M6">
+            <v>1</v>
+          </cell>
+          <cell r="N6">
+            <v>1</v>
+          </cell>
+          <cell r="O6">
+            <v>6</v>
+          </cell>
+          <cell r="P6">
+            <v>1</v>
+          </cell>
+          <cell r="Q6">
+            <v>5</v>
+          </cell>
+          <cell r="R6">
+            <v>100</v>
           </cell>
         </row>
         <row r="7">
           <cell r="B7" t="str">
-            <v>Atchutapuram</v>
+            <v>Anakapalli Traffic</v>
           </cell>
           <cell r="C7">
             <v>1</v>
           </cell>
-          <cell r="D7">
-            <v>1</v>
-          </cell>
           <cell r="E7">
-            <v>100</v>
+            <v>1</v>
           </cell>
           <cell r="F7">
-            <v>10</v>
+            <v>1</v>
+          </cell>
+          <cell r="H7">
+            <v>1</v>
+          </cell>
+          <cell r="I7">
+            <v>1</v>
+          </cell>
+          <cell r="J7">
+            <v>1</v>
+          </cell>
+          <cell r="K7">
+            <v>1</v>
+          </cell>
+          <cell r="L7">
+            <v>1</v>
+          </cell>
+          <cell r="M7">
+            <v>1</v>
+          </cell>
+          <cell r="N7">
+            <v>1</v>
+          </cell>
+          <cell r="Q7">
+            <v>3.5714285714285716</v>
+          </cell>
+          <cell r="R7">
+            <v>71.428571428571431</v>
           </cell>
         </row>
         <row r="8">
           <cell r="B8" t="str">
-            <v>Butchiyyapeta</v>
-          </cell>
-          <cell r="E8">
-            <v>100</v>
-          </cell>
-          <cell r="F8">
-            <v>10</v>
+            <v>Atchutapuram</v>
+          </cell>
+          <cell r="G8">
+            <v>1</v>
+          </cell>
+          <cell r="K8">
+            <v>1</v>
+          </cell>
+          <cell r="M8">
+            <v>1</v>
+          </cell>
+          <cell r="O8">
+            <v>1</v>
+          </cell>
+          <cell r="Q8">
+            <v>1.4285714285714286</v>
+          </cell>
+          <cell r="R8">
+            <v>28.571428571428569</v>
           </cell>
         </row>
         <row r="9">
           <cell r="B9" t="str">
-            <v>Cheedikada</v>
-          </cell>
-          <cell r="E9">
-            <v>100</v>
-          </cell>
-          <cell r="F9">
-            <v>10</v>
+            <v>Butchiyyapeta</v>
+          </cell>
+          <cell r="C9">
+            <v>3</v>
+          </cell>
+          <cell r="G9">
+            <v>2</v>
+          </cell>
+          <cell r="J9">
+            <v>1</v>
+          </cell>
+          <cell r="M9">
+            <v>3</v>
+          </cell>
+          <cell r="O9">
+            <v>1</v>
+          </cell>
+          <cell r="Q9">
+            <v>1.7857142857142858</v>
+          </cell>
+          <cell r="R9">
+            <v>35.714285714285715</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10" t="str">
-            <v>Chodavaram</v>
-          </cell>
-          <cell r="E10">
-            <v>100</v>
-          </cell>
-          <cell r="F10">
-            <v>10</v>
+            <v>Cheedikada</v>
+          </cell>
+          <cell r="C10">
+            <v>1</v>
+          </cell>
+          <cell r="Q10">
+            <v>0.35714285714285715</v>
+          </cell>
+          <cell r="R10">
+            <v>7.1428571428571423</v>
           </cell>
         </row>
         <row r="11">
           <cell r="B11" t="str">
-            <v>Devarapalli</v>
+            <v>Chodavaram</v>
+          </cell>
+          <cell r="C11">
+            <v>4</v>
+          </cell>
+          <cell r="D11">
+            <v>1</v>
           </cell>
           <cell r="E11">
-            <v>100</v>
+            <v>1</v>
           </cell>
           <cell r="F11">
-            <v>10</v>
+            <v>1</v>
+          </cell>
+          <cell r="G11">
+            <v>1</v>
+          </cell>
+          <cell r="I11">
+            <v>1</v>
+          </cell>
+          <cell r="J11">
+            <v>1</v>
+          </cell>
+          <cell r="K11">
+            <v>1</v>
+          </cell>
+          <cell r="M11">
+            <v>1</v>
+          </cell>
+          <cell r="N11">
+            <v>1</v>
+          </cell>
+          <cell r="Q11">
+            <v>3.5714285714285716</v>
+          </cell>
+          <cell r="R11">
+            <v>71.428571428571431</v>
           </cell>
         </row>
         <row r="12">
           <cell r="B12" t="str">
-            <v>Golugonda</v>
-          </cell>
-          <cell r="E12">
-            <v>100</v>
-          </cell>
-          <cell r="F12">
-            <v>10</v>
+            <v>Devarapalli</v>
+          </cell>
+          <cell r="K12">
+            <v>1</v>
+          </cell>
+          <cell r="M12">
+            <v>1</v>
+          </cell>
+          <cell r="Q12">
+            <v>0.7142857142857143</v>
+          </cell>
+          <cell r="R12">
+            <v>14.285714285714285</v>
           </cell>
         </row>
         <row r="13">
           <cell r="B13" t="str">
-            <v>K.D.Peta</v>
+            <v>Golugonda</v>
+          </cell>
+          <cell r="C13">
+            <v>1</v>
+          </cell>
+          <cell r="D13">
+            <v>1</v>
           </cell>
           <cell r="E13">
-            <v>100</v>
+            <v>1</v>
           </cell>
           <cell r="F13">
-            <v>10</v>
+            <v>1</v>
+          </cell>
+          <cell r="G13">
+            <v>1</v>
+          </cell>
+          <cell r="H13">
+            <v>1</v>
+          </cell>
+          <cell r="J13">
+            <v>1</v>
+          </cell>
+          <cell r="L13">
+            <v>1</v>
+          </cell>
+          <cell r="M13">
+            <v>1</v>
+          </cell>
+          <cell r="N13">
+            <v>1</v>
+          </cell>
+          <cell r="O13">
+            <v>1</v>
+          </cell>
+          <cell r="Q13">
+            <v>3.9285714285714284</v>
+          </cell>
+          <cell r="R13">
+            <v>78.571428571428569</v>
           </cell>
         </row>
         <row r="14">
           <cell r="B14" t="str">
-            <v>K.Kotapadu</v>
-          </cell>
-          <cell r="E14">
-            <v>100</v>
-          </cell>
-          <cell r="F14">
-            <v>10</v>
+            <v>K.D.Peta</v>
+          </cell>
+          <cell r="N14">
+            <v>1</v>
+          </cell>
+          <cell r="Q14">
+            <v>0.35714285714285715</v>
+          </cell>
+          <cell r="R14">
+            <v>7.1428571428571423</v>
           </cell>
         </row>
         <row r="15">
           <cell r="B15" t="str">
-            <v>Kasimkota</v>
-          </cell>
-          <cell r="C15">
-            <v>2</v>
-          </cell>
-          <cell r="D15">
-            <v>0</v>
-          </cell>
-          <cell r="E15">
-            <v>0</v>
-          </cell>
-          <cell r="F15">
-            <v>0</v>
+            <v>K.Kotapadu</v>
+          </cell>
+          <cell r="I15">
+            <v>3</v>
+          </cell>
+          <cell r="Q15">
+            <v>0.35714285714285715</v>
+          </cell>
+          <cell r="R15">
+            <v>7.1428571428571423</v>
           </cell>
         </row>
         <row r="16">
           <cell r="B16" t="str">
-            <v>Kotavurtla</v>
+            <v>Kasimkota</v>
+          </cell>
+          <cell r="C16">
+            <v>1</v>
           </cell>
           <cell r="E16">
-            <v>100</v>
-          </cell>
-          <cell r="F16">
-            <v>10</v>
+            <v>1</v>
+          </cell>
+          <cell r="G16">
+            <v>2</v>
+          </cell>
+          <cell r="H16">
+            <v>1</v>
+          </cell>
+          <cell r="I16">
+            <v>1</v>
+          </cell>
+          <cell r="K16">
+            <v>1</v>
+          </cell>
+          <cell r="L16">
+            <v>1</v>
+          </cell>
+          <cell r="M16">
+            <v>1</v>
+          </cell>
+          <cell r="O16">
+            <v>1</v>
+          </cell>
+          <cell r="Q16">
+            <v>3.2142857142857144</v>
+          </cell>
+          <cell r="R16">
+            <v>64.285714285714292</v>
           </cell>
         </row>
         <row r="17">
           <cell r="B17" t="str">
-            <v>Kothakota</v>
+            <v>Kotavurtla</v>
           </cell>
           <cell r="C17">
-            <v>1</v>
+            <v>3</v>
           </cell>
           <cell r="D17">
             <v>1</v>
           </cell>
           <cell r="E17">
-            <v>100</v>
+            <v>1</v>
           </cell>
           <cell r="F17">
-            <v>10</v>
+            <v>1</v>
+          </cell>
+          <cell r="G17">
+            <v>1</v>
+          </cell>
+          <cell r="H17">
+            <v>1</v>
+          </cell>
+          <cell r="I17">
+            <v>26</v>
+          </cell>
+          <cell r="J17">
+            <v>1</v>
+          </cell>
+          <cell r="K17">
+            <v>1</v>
+          </cell>
+          <cell r="L17">
+            <v>1</v>
+          </cell>
+          <cell r="M17">
+            <v>1</v>
+          </cell>
+          <cell r="N17">
+            <v>1</v>
+          </cell>
+          <cell r="O17">
+            <v>1</v>
+          </cell>
+          <cell r="P17">
+            <v>1</v>
+          </cell>
+          <cell r="Q17">
+            <v>5</v>
+          </cell>
+          <cell r="R17">
+            <v>100</v>
           </cell>
         </row>
         <row r="18">
           <cell r="B18" t="str">
-            <v>Mahila UPS, Anakapalli</v>
-          </cell>
-          <cell r="E18">
-            <v>100</v>
-          </cell>
-          <cell r="F18">
-            <v>10</v>
+            <v>Kothakota</v>
+          </cell>
+          <cell r="Q18">
+            <v>0</v>
+          </cell>
+          <cell r="R18">
+            <v>0</v>
           </cell>
         </row>
         <row r="19">
           <cell r="B19" t="str">
-            <v>Makavarapalem</v>
-          </cell>
-          <cell r="E19">
-            <v>100</v>
-          </cell>
-          <cell r="F19">
-            <v>10</v>
+            <v>Mahila UPS, Anakapalli</v>
+          </cell>
+          <cell r="Q19">
+            <v>0</v>
+          </cell>
+          <cell r="R19">
+            <v>0</v>
           </cell>
         </row>
         <row r="20">
           <cell r="B20" t="str">
-            <v>Munagapaka</v>
-          </cell>
-          <cell r="E20">
-            <v>100</v>
-          </cell>
-          <cell r="F20">
-            <v>10</v>
+            <v>Makavarapalem</v>
+          </cell>
+          <cell r="Q20">
+            <v>0</v>
+          </cell>
+          <cell r="R20">
+            <v>0</v>
           </cell>
         </row>
         <row r="21">
           <cell r="B21" t="str">
-            <v>Nakkapalli</v>
+            <v>Munagapaka</v>
+          </cell>
+          <cell r="C21">
+            <v>2</v>
+          </cell>
+          <cell r="D21">
+            <v>1</v>
           </cell>
           <cell r="E21">
-            <v>100</v>
+            <v>4</v>
           </cell>
           <cell r="F21">
-            <v>10</v>
+            <v>1</v>
+          </cell>
+          <cell r="G21">
+            <v>6</v>
+          </cell>
+          <cell r="I21">
+            <v>1</v>
+          </cell>
+          <cell r="J21">
+            <v>1</v>
+          </cell>
+          <cell r="K21">
+            <v>3</v>
+          </cell>
+          <cell r="M21">
+            <v>2</v>
+          </cell>
+          <cell r="N21">
+            <v>1</v>
+          </cell>
+          <cell r="Q21">
+            <v>3.5714285714285716</v>
+          </cell>
+          <cell r="R21">
+            <v>71.428571428571431</v>
           </cell>
         </row>
         <row r="22">
           <cell r="B22" t="str">
-            <v>Narsipatnam Rural</v>
-          </cell>
-          <cell r="E22">
-            <v>100</v>
-          </cell>
-          <cell r="F22">
-            <v>10</v>
+            <v>Nakkapalli</v>
+          </cell>
+          <cell r="Q22">
+            <v>0</v>
+          </cell>
+          <cell r="R22">
+            <v>0</v>
           </cell>
         </row>
         <row r="23">
           <cell r="B23" t="str">
-            <v>Narsipatnam Town</v>
-          </cell>
-          <cell r="E23">
-            <v>100</v>
-          </cell>
-          <cell r="F23">
-            <v>10</v>
+            <v>Narsipatnam Rural</v>
+          </cell>
+          <cell r="Q23">
+            <v>0</v>
+          </cell>
+          <cell r="R23">
+            <v>0</v>
           </cell>
         </row>
         <row r="24">
           <cell r="B24" t="str">
-            <v>Nathavaram</v>
+            <v>Narsipatnam Town</v>
           </cell>
           <cell r="C24">
             <v>1</v>
@@ -15293,98 +15667,239 @@
             <v>1</v>
           </cell>
           <cell r="E24">
-            <v>100</v>
+            <v>1</v>
           </cell>
           <cell r="F24">
-            <v>10</v>
+            <v>1</v>
+          </cell>
+          <cell r="G24">
+            <v>1</v>
+          </cell>
+          <cell r="H24">
+            <v>1</v>
+          </cell>
+          <cell r="I24">
+            <v>2</v>
+          </cell>
+          <cell r="J24">
+            <v>1</v>
+          </cell>
+          <cell r="K24">
+            <v>1</v>
+          </cell>
+          <cell r="L24">
+            <v>1</v>
+          </cell>
+          <cell r="M24">
+            <v>1</v>
+          </cell>
+          <cell r="N24">
+            <v>1</v>
+          </cell>
+          <cell r="Q24">
+            <v>4.2857142857142856</v>
+          </cell>
+          <cell r="R24">
+            <v>85.714285714285708</v>
           </cell>
         </row>
         <row r="25">
           <cell r="B25" t="str">
-            <v>Parawada</v>
+            <v>Nathavaram</v>
+          </cell>
+          <cell r="C25">
+            <v>1</v>
+          </cell>
+          <cell r="D25">
+            <v>1</v>
           </cell>
           <cell r="E25">
-            <v>100</v>
+            <v>1</v>
           </cell>
           <cell r="F25">
-            <v>10</v>
+            <v>1</v>
+          </cell>
+          <cell r="H25">
+            <v>1</v>
+          </cell>
+          <cell r="J25">
+            <v>1</v>
+          </cell>
+          <cell r="K25">
+            <v>1</v>
+          </cell>
+          <cell r="L25">
+            <v>1</v>
+          </cell>
+          <cell r="O25">
+            <v>2</v>
+          </cell>
+          <cell r="Q25">
+            <v>3.2142857142857144</v>
+          </cell>
+          <cell r="R25">
+            <v>64.285714285714292</v>
           </cell>
         </row>
         <row r="26">
           <cell r="B26" t="str">
-            <v>Payakaraopeta</v>
-          </cell>
-          <cell r="E26">
-            <v>100</v>
+            <v>Parawada</v>
+          </cell>
+          <cell r="C26">
+            <v>1</v>
+          </cell>
+          <cell r="D26">
+            <v>1</v>
           </cell>
           <cell r="F26">
-            <v>10</v>
+            <v>1</v>
+          </cell>
+          <cell r="G26">
+            <v>1</v>
+          </cell>
+          <cell r="I26">
+            <v>1</v>
+          </cell>
+          <cell r="K26">
+            <v>1</v>
+          </cell>
+          <cell r="L26">
+            <v>1</v>
+          </cell>
+          <cell r="N26">
+            <v>1</v>
+          </cell>
+          <cell r="O26">
+            <v>1</v>
+          </cell>
+          <cell r="Q26">
+            <v>3.2142857142857144</v>
+          </cell>
+          <cell r="R26">
+            <v>64.285714285714292</v>
           </cell>
         </row>
         <row r="27">
           <cell r="B27" t="str">
-            <v>Rambilli</v>
+            <v>Payakaraopeta</v>
+          </cell>
+          <cell r="C27">
+            <v>1</v>
+          </cell>
+          <cell r="D27">
+            <v>1</v>
           </cell>
           <cell r="E27">
-            <v>100</v>
+            <v>1</v>
           </cell>
           <cell r="F27">
-            <v>10</v>
+            <v>1</v>
+          </cell>
+          <cell r="G27">
+            <v>2</v>
+          </cell>
+          <cell r="H27">
+            <v>1</v>
+          </cell>
+          <cell r="I27">
+            <v>1</v>
+          </cell>
+          <cell r="J27">
+            <v>1</v>
+          </cell>
+          <cell r="K27">
+            <v>1</v>
+          </cell>
+          <cell r="L27">
+            <v>1</v>
+          </cell>
+          <cell r="M27">
+            <v>1</v>
+          </cell>
+          <cell r="O27">
+            <v>4</v>
+          </cell>
+          <cell r="Q27">
+            <v>4.2857142857142856</v>
+          </cell>
+          <cell r="R27">
+            <v>85.714285714285708</v>
           </cell>
         </row>
         <row r="28">
           <cell r="B28" t="str">
-            <v>Ravikamatham</v>
-          </cell>
-          <cell r="E28">
-            <v>100</v>
-          </cell>
-          <cell r="F28">
-            <v>10</v>
+            <v>Rambilli</v>
+          </cell>
+          <cell r="G28">
+            <v>1</v>
+          </cell>
+          <cell r="I28">
+            <v>1</v>
+          </cell>
+          <cell r="Q28">
+            <v>0.7142857142857143</v>
+          </cell>
+          <cell r="R28">
+            <v>14.285714285714285</v>
           </cell>
         </row>
         <row r="29">
           <cell r="B29" t="str">
-            <v>Rolugunta</v>
-          </cell>
-          <cell r="E29">
-            <v>100</v>
-          </cell>
-          <cell r="F29">
-            <v>10</v>
+            <v>Ravikamatham</v>
+          </cell>
+          <cell r="Q29">
+            <v>0</v>
+          </cell>
+          <cell r="R29">
+            <v>0</v>
           </cell>
         </row>
         <row r="30">
           <cell r="B30" t="str">
-            <v>S.Rayavaram</v>
-          </cell>
-          <cell r="C30">
-            <v>1</v>
-          </cell>
-          <cell r="D30">
-            <v>1</v>
-          </cell>
-          <cell r="E30">
-            <v>100</v>
-          </cell>
-          <cell r="F30">
-            <v>10</v>
+            <v>Rolugunta</v>
+          </cell>
+          <cell r="Q30">
+            <v>0</v>
+          </cell>
+          <cell r="R30">
+            <v>0</v>
           </cell>
         </row>
         <row r="31">
           <cell r="B31" t="str">
-            <v>Sabbavaram</v>
-          </cell>
-          <cell r="E31">
-            <v>100</v>
+            <v>S.Rayavaram</v>
+          </cell>
+          <cell r="C31">
+            <v>1</v>
           </cell>
           <cell r="F31">
-            <v>10</v>
+            <v>1</v>
+          </cell>
+          <cell r="H31">
+            <v>1</v>
+          </cell>
+          <cell r="J31">
+            <v>1</v>
+          </cell>
+          <cell r="L31">
+            <v>1</v>
+          </cell>
+          <cell r="N31">
+            <v>1</v>
+          </cell>
+          <cell r="O31">
+            <v>1</v>
+          </cell>
+          <cell r="Q31">
+            <v>2.5</v>
+          </cell>
+          <cell r="R31">
+            <v>50</v>
           </cell>
         </row>
         <row r="32">
           <cell r="B32" t="str">
-            <v>V.Madugula</v>
+            <v>Sabbavaram</v>
           </cell>
           <cell r="C32">
             <v>1</v>
@@ -15393,711 +15908,519 @@
             <v>1</v>
           </cell>
           <cell r="E32">
-            <v>100</v>
+            <v>2</v>
           </cell>
           <cell r="F32">
-            <v>10</v>
+            <v>1</v>
+          </cell>
+          <cell r="G32">
+            <v>1</v>
+          </cell>
+          <cell r="H32">
+            <v>1</v>
+          </cell>
+          <cell r="I32">
+            <v>1</v>
+          </cell>
+          <cell r="J32">
+            <v>1</v>
+          </cell>
+          <cell r="K32">
+            <v>1</v>
+          </cell>
+          <cell r="L32">
+            <v>1</v>
+          </cell>
+          <cell r="M32">
+            <v>1</v>
+          </cell>
+          <cell r="N32">
+            <v>1</v>
+          </cell>
+          <cell r="O32">
+            <v>1</v>
+          </cell>
+          <cell r="P32">
+            <v>1</v>
+          </cell>
+          <cell r="Q32">
+            <v>5</v>
+          </cell>
+          <cell r="R32">
+            <v>100</v>
           </cell>
         </row>
         <row r="33">
           <cell r="B33" t="str">
-            <v>Yelamanchili Rural</v>
-          </cell>
-          <cell r="C33">
-            <v>1</v>
+            <v>V.Madugula</v>
           </cell>
           <cell r="D33">
             <v>1</v>
           </cell>
-          <cell r="E33">
-            <v>100</v>
-          </cell>
-          <cell r="F33">
-            <v>10</v>
+          <cell r="I33">
+            <v>1</v>
+          </cell>
+          <cell r="M33">
+            <v>2</v>
+          </cell>
+          <cell r="O33">
+            <v>1</v>
+          </cell>
+          <cell r="Q33">
+            <v>1.4285714285714286</v>
+          </cell>
+          <cell r="R33">
+            <v>28.571428571428569</v>
           </cell>
         </row>
         <row r="34">
           <cell r="B34" t="str">
-            <v>Yelamanchili Town</v>
+            <v>Yelamanchili Rural</v>
+          </cell>
+          <cell r="C34">
+            <v>1</v>
+          </cell>
+          <cell r="D34">
+            <v>1</v>
           </cell>
           <cell r="E34">
-            <v>100</v>
+            <v>1</v>
           </cell>
           <cell r="F34">
-            <v>10</v>
+            <v>1</v>
+          </cell>
+          <cell r="G34">
+            <v>1</v>
+          </cell>
+          <cell r="H34">
+            <v>1</v>
+          </cell>
+          <cell r="J34">
+            <v>1</v>
+          </cell>
+          <cell r="K34">
+            <v>1</v>
+          </cell>
+          <cell r="L34">
+            <v>1</v>
+          </cell>
+          <cell r="N34">
+            <v>1</v>
+          </cell>
+          <cell r="O34">
+            <v>1</v>
+          </cell>
+          <cell r="Q34">
+            <v>3.9285714285714284</v>
+          </cell>
+          <cell r="R34">
+            <v>78.571428571428569</v>
           </cell>
         </row>
         <row r="35">
           <cell r="B35" t="str">
+            <v>Yelamanchili Town</v>
+          </cell>
+          <cell r="C35">
+            <v>1</v>
+          </cell>
+          <cell r="D35">
+            <v>1</v>
+          </cell>
+          <cell r="E35">
+            <v>2</v>
+          </cell>
+          <cell r="F35">
+            <v>1</v>
+          </cell>
+          <cell r="G35">
+            <v>1</v>
+          </cell>
+          <cell r="H35">
+            <v>1</v>
+          </cell>
+          <cell r="I35">
+            <v>1</v>
+          </cell>
+          <cell r="J35">
+            <v>1</v>
+          </cell>
+          <cell r="M35">
+            <v>2</v>
+          </cell>
+          <cell r="O35">
+            <v>6</v>
+          </cell>
+          <cell r="Q35">
+            <v>3.5714285714285716</v>
+          </cell>
+          <cell r="R35">
+            <v>71.428571428571431</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="B36" t="str">
             <v>Yelamanchili Traffic</v>
           </cell>
-          <cell r="E35">
-            <v>100</v>
-          </cell>
-          <cell r="F35">
-            <v>10</v>
-          </cell>
-        </row>
-        <row r="36">
           <cell r="C36">
-            <v>8</v>
-          </cell>
-          <cell r="D36">
-            <v>6</v>
+            <v>1</v>
           </cell>
           <cell r="E36">
-            <v>96.969696969696969</v>
+            <v>1</v>
           </cell>
           <cell r="F36">
-            <v>9.6969696969696972</v>
+            <v>1</v>
+          </cell>
+          <cell r="G36">
+            <v>1</v>
+          </cell>
+          <cell r="H36">
+            <v>1</v>
+          </cell>
+          <cell r="J36">
+            <v>1</v>
+          </cell>
+          <cell r="K36">
+            <v>1</v>
+          </cell>
+          <cell r="L36">
+            <v>1</v>
+          </cell>
+          <cell r="N36">
+            <v>1</v>
+          </cell>
+          <cell r="O36">
+            <v>1</v>
+          </cell>
+          <cell r="Q36">
+            <v>3.5714285714285716</v>
+          </cell>
+          <cell r="R36">
+            <v>71.428571428571431</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="C37">
+            <v>32</v>
+          </cell>
+          <cell r="D37">
+            <v>14</v>
+          </cell>
+          <cell r="E37">
+            <v>22</v>
+          </cell>
+          <cell r="F37">
+            <v>17</v>
+          </cell>
+          <cell r="G37">
+            <v>25</v>
+          </cell>
+          <cell r="H37">
+            <v>15</v>
+          </cell>
+          <cell r="I37">
+            <v>45</v>
+          </cell>
+          <cell r="J37">
+            <v>17</v>
+          </cell>
+          <cell r="K37">
+            <v>19</v>
+          </cell>
+          <cell r="L37">
+            <v>14</v>
+          </cell>
+          <cell r="M37">
+            <v>26</v>
+          </cell>
+          <cell r="N37">
+            <v>15</v>
+          </cell>
+          <cell r="O37">
+            <v>31</v>
+          </cell>
+          <cell r="P37">
+            <v>3</v>
+          </cell>
+          <cell r="Q37">
+            <v>2.3268398268398265</v>
+          </cell>
+          <cell r="R37">
+            <v>46.53679653679653</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="17">
         <row r="2">
           <cell r="B2" t="str">
-            <v>PS</v>
-          </cell>
-          <cell r="C2">
-            <v>46281</v>
-          </cell>
-          <cell r="E2">
-            <v>46281</v>
-          </cell>
-          <cell r="G2">
-            <v>2</v>
-          </cell>
-          <cell r="I2">
-            <v>3</v>
-          </cell>
-          <cell r="K2">
-            <v>4</v>
-          </cell>
-          <cell r="M2">
-            <v>5</v>
-          </cell>
-          <cell r="O2">
-            <v>6</v>
-          </cell>
-          <cell r="Q2" t="str">
-            <v>MARKS</v>
-          </cell>
-          <cell r="R2" t="str">
-            <v>RAW VALUE</v>
+            <v>PS Name</v>
+          </cell>
+          <cell r="C2" t="str">
+            <v xml:space="preserve">Total FIRS 
+Registered </v>
+          </cell>
+          <cell r="D2" t="str">
+            <v>Total FORM1 Uploads</v>
+          </cell>
+          <cell r="E2" t="str">
+            <v>Raw Value</v>
+          </cell>
+          <cell r="F2" t="str">
+            <v>Marks</v>
           </cell>
         </row>
         <row r="3">
-          <cell r="C3" t="str">
-            <v>WEB</v>
-          </cell>
-          <cell r="D3" t="str">
-            <v>MOBILE</v>
-          </cell>
-          <cell r="E3" t="str">
-            <v>WEB</v>
-          </cell>
-          <cell r="F3" t="str">
-            <v>MOBILE</v>
-          </cell>
-          <cell r="G3" t="str">
-            <v>WEB</v>
-          </cell>
-          <cell r="H3" t="str">
-            <v>MOBILE</v>
-          </cell>
-          <cell r="I3" t="str">
-            <v>WEB</v>
-          </cell>
-          <cell r="J3" t="str">
-            <v>MOBILE</v>
-          </cell>
-          <cell r="K3" t="str">
-            <v>WEB</v>
-          </cell>
-          <cell r="L3" t="str">
-            <v>MOBILE</v>
-          </cell>
-          <cell r="M3" t="str">
-            <v>WEB</v>
-          </cell>
-          <cell r="N3" t="str">
-            <v>MOBILE</v>
-          </cell>
-          <cell r="O3" t="str">
-            <v>WEB</v>
-          </cell>
-          <cell r="P3" t="str">
-            <v>MOBILE</v>
+          <cell r="B3" t="str">
+            <v>A.Koduru</v>
+          </cell>
+          <cell r="E3">
+            <v>100</v>
+          </cell>
+          <cell r="F3">
+            <v>10</v>
           </cell>
         </row>
         <row r="4">
           <cell r="B4" t="str">
-            <v>A.Koduru</v>
-          </cell>
-          <cell r="C4">
-            <v>1</v>
+            <v>Anakapalli Rural</v>
           </cell>
           <cell r="E4">
-            <v>1</v>
+            <v>100</v>
           </cell>
           <cell r="F4">
-            <v>1</v>
-          </cell>
-          <cell r="H4">
-            <v>1</v>
-          </cell>
-          <cell r="I4">
-            <v>1</v>
-          </cell>
-          <cell r="J4">
-            <v>1</v>
-          </cell>
-          <cell r="K4">
-            <v>1</v>
-          </cell>
-          <cell r="M4">
-            <v>1</v>
-          </cell>
-          <cell r="N4">
-            <v>1</v>
-          </cell>
-          <cell r="O4">
-            <v>1</v>
-          </cell>
-          <cell r="Q4">
-            <v>3.5714285714285716</v>
-          </cell>
-          <cell r="R4">
-            <v>71.428571428571431</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="5">
           <cell r="B5" t="str">
-            <v>Anakapalli Rural</v>
-          </cell>
-          <cell r="C5">
-            <v>4</v>
-          </cell>
-          <cell r="D5">
-            <v>1</v>
+            <v>Anakapalli Town</v>
           </cell>
           <cell r="E5">
-            <v>1</v>
+            <v>100</v>
           </cell>
           <cell r="F5">
-            <v>1</v>
-          </cell>
-          <cell r="G5">
-            <v>1</v>
-          </cell>
-          <cell r="H5">
-            <v>1</v>
-          </cell>
-          <cell r="I5">
-            <v>1</v>
-          </cell>
-          <cell r="J5">
-            <v>1</v>
-          </cell>
-          <cell r="K5">
-            <v>1</v>
-          </cell>
-          <cell r="L5">
-            <v>1</v>
-          </cell>
-          <cell r="M5">
-            <v>5</v>
-          </cell>
-          <cell r="N5">
-            <v>1</v>
-          </cell>
-          <cell r="O5">
-            <v>1</v>
-          </cell>
-          <cell r="Q5">
-            <v>4.6428571428571432</v>
-          </cell>
-          <cell r="R5">
-            <v>92.857142857142861</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="6">
           <cell r="B6" t="str">
-            <v>Anakapalli Town</v>
-          </cell>
-          <cell r="C6">
-            <v>2</v>
-          </cell>
-          <cell r="D6">
-            <v>1</v>
+            <v>Anakapalli Traffic</v>
           </cell>
           <cell r="E6">
-            <v>2</v>
+            <v>100</v>
           </cell>
           <cell r="F6">
-            <v>1</v>
-          </cell>
-          <cell r="G6">
-            <v>1</v>
-          </cell>
-          <cell r="H6">
-            <v>1</v>
-          </cell>
-          <cell r="I6">
-            <v>2</v>
-          </cell>
-          <cell r="J6">
-            <v>1</v>
-          </cell>
-          <cell r="K6">
-            <v>1</v>
-          </cell>
-          <cell r="L6">
-            <v>1</v>
-          </cell>
-          <cell r="M6">
-            <v>1</v>
-          </cell>
-          <cell r="N6">
-            <v>1</v>
-          </cell>
-          <cell r="O6">
-            <v>6</v>
-          </cell>
-          <cell r="P6">
-            <v>1</v>
-          </cell>
-          <cell r="Q6">
-            <v>5</v>
-          </cell>
-          <cell r="R6">
-            <v>100</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="7">
           <cell r="B7" t="str">
-            <v>Anakapalli Traffic</v>
+            <v>Atchutapuram</v>
           </cell>
           <cell r="C7">
             <v>1</v>
           </cell>
+          <cell r="D7">
+            <v>1</v>
+          </cell>
           <cell r="E7">
-            <v>1</v>
+            <v>100</v>
           </cell>
           <cell r="F7">
-            <v>1</v>
-          </cell>
-          <cell r="H7">
-            <v>1</v>
-          </cell>
-          <cell r="I7">
-            <v>1</v>
-          </cell>
-          <cell r="J7">
-            <v>1</v>
-          </cell>
-          <cell r="K7">
-            <v>1</v>
-          </cell>
-          <cell r="L7">
-            <v>1</v>
-          </cell>
-          <cell r="M7">
-            <v>1</v>
-          </cell>
-          <cell r="N7">
-            <v>1</v>
-          </cell>
-          <cell r="Q7">
-            <v>3.5714285714285716</v>
-          </cell>
-          <cell r="R7">
-            <v>71.428571428571431</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="8">
           <cell r="B8" t="str">
-            <v>Atchutapuram</v>
-          </cell>
-          <cell r="G8">
-            <v>1</v>
-          </cell>
-          <cell r="K8">
-            <v>1</v>
-          </cell>
-          <cell r="M8">
-            <v>1</v>
-          </cell>
-          <cell r="O8">
-            <v>1</v>
-          </cell>
-          <cell r="Q8">
-            <v>1.4285714285714286</v>
-          </cell>
-          <cell r="R8">
-            <v>28.571428571428569</v>
+            <v>Butchiyyapeta</v>
+          </cell>
+          <cell r="E8">
+            <v>100</v>
+          </cell>
+          <cell r="F8">
+            <v>10</v>
           </cell>
         </row>
         <row r="9">
           <cell r="B9" t="str">
-            <v>Butchiyyapeta</v>
-          </cell>
-          <cell r="C9">
-            <v>3</v>
-          </cell>
-          <cell r="G9">
-            <v>2</v>
-          </cell>
-          <cell r="J9">
-            <v>1</v>
-          </cell>
-          <cell r="M9">
-            <v>3</v>
-          </cell>
-          <cell r="O9">
-            <v>1</v>
-          </cell>
-          <cell r="Q9">
-            <v>1.7857142857142858</v>
-          </cell>
-          <cell r="R9">
-            <v>35.714285714285715</v>
+            <v>Cheedikada</v>
+          </cell>
+          <cell r="E9">
+            <v>100</v>
+          </cell>
+          <cell r="F9">
+            <v>10</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10" t="str">
-            <v>Cheedikada</v>
-          </cell>
-          <cell r="C10">
-            <v>1</v>
-          </cell>
-          <cell r="Q10">
-            <v>0.35714285714285715</v>
-          </cell>
-          <cell r="R10">
-            <v>7.1428571428571423</v>
+            <v>Chodavaram</v>
+          </cell>
+          <cell r="E10">
+            <v>100</v>
+          </cell>
+          <cell r="F10">
+            <v>10</v>
           </cell>
         </row>
         <row r="11">
           <cell r="B11" t="str">
-            <v>Chodavaram</v>
-          </cell>
-          <cell r="C11">
-            <v>4</v>
-          </cell>
-          <cell r="D11">
-            <v>1</v>
+            <v>Devarapalli</v>
           </cell>
           <cell r="E11">
-            <v>1</v>
+            <v>100</v>
           </cell>
           <cell r="F11">
-            <v>1</v>
-          </cell>
-          <cell r="G11">
-            <v>1</v>
-          </cell>
-          <cell r="I11">
-            <v>1</v>
-          </cell>
-          <cell r="J11">
-            <v>1</v>
-          </cell>
-          <cell r="K11">
-            <v>1</v>
-          </cell>
-          <cell r="M11">
-            <v>1</v>
-          </cell>
-          <cell r="N11">
-            <v>1</v>
-          </cell>
-          <cell r="Q11">
-            <v>3.5714285714285716</v>
-          </cell>
-          <cell r="R11">
-            <v>71.428571428571431</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="12">
           <cell r="B12" t="str">
-            <v>Devarapalli</v>
-          </cell>
-          <cell r="K12">
-            <v>1</v>
-          </cell>
-          <cell r="M12">
-            <v>1</v>
-          </cell>
-          <cell r="Q12">
-            <v>0.7142857142857143</v>
-          </cell>
-          <cell r="R12">
-            <v>14.285714285714285</v>
+            <v>Golugonda</v>
+          </cell>
+          <cell r="E12">
+            <v>100</v>
+          </cell>
+          <cell r="F12">
+            <v>10</v>
           </cell>
         </row>
         <row r="13">
           <cell r="B13" t="str">
-            <v>Golugonda</v>
-          </cell>
-          <cell r="C13">
-            <v>1</v>
-          </cell>
-          <cell r="D13">
-            <v>1</v>
+            <v>K.D.Peta</v>
           </cell>
           <cell r="E13">
-            <v>1</v>
+            <v>100</v>
           </cell>
           <cell r="F13">
-            <v>1</v>
-          </cell>
-          <cell r="G13">
-            <v>1</v>
-          </cell>
-          <cell r="H13">
-            <v>1</v>
-          </cell>
-          <cell r="J13">
-            <v>1</v>
-          </cell>
-          <cell r="L13">
-            <v>1</v>
-          </cell>
-          <cell r="M13">
-            <v>1</v>
-          </cell>
-          <cell r="N13">
-            <v>1</v>
-          </cell>
-          <cell r="O13">
-            <v>1</v>
-          </cell>
-          <cell r="Q13">
-            <v>3.9285714285714284</v>
-          </cell>
-          <cell r="R13">
-            <v>78.571428571428569</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="14">
           <cell r="B14" t="str">
-            <v>K.D.Peta</v>
-          </cell>
-          <cell r="N14">
-            <v>1</v>
-          </cell>
-          <cell r="Q14">
-            <v>0.35714285714285715</v>
-          </cell>
-          <cell r="R14">
-            <v>7.1428571428571423</v>
+            <v>K.Kotapadu</v>
+          </cell>
+          <cell r="E14">
+            <v>100</v>
+          </cell>
+          <cell r="F14">
+            <v>10</v>
           </cell>
         </row>
         <row r="15">
           <cell r="B15" t="str">
-            <v>K.Kotapadu</v>
-          </cell>
-          <cell r="I15">
-            <v>3</v>
-          </cell>
-          <cell r="Q15">
-            <v>0.35714285714285715</v>
-          </cell>
-          <cell r="R15">
-            <v>7.1428571428571423</v>
+            <v>Kasimkota</v>
+          </cell>
+          <cell r="C15">
+            <v>2</v>
+          </cell>
+          <cell r="D15">
+            <v>0</v>
+          </cell>
+          <cell r="E15">
+            <v>0</v>
+          </cell>
+          <cell r="F15">
+            <v>0</v>
           </cell>
         </row>
         <row r="16">
           <cell r="B16" t="str">
-            <v>Kasimkota</v>
-          </cell>
-          <cell r="C16">
-            <v>1</v>
+            <v>Kotavurtla</v>
           </cell>
           <cell r="E16">
-            <v>1</v>
-          </cell>
-          <cell r="G16">
-            <v>2</v>
-          </cell>
-          <cell r="H16">
-            <v>1</v>
-          </cell>
-          <cell r="I16">
-            <v>1</v>
-          </cell>
-          <cell r="K16">
-            <v>1</v>
-          </cell>
-          <cell r="L16">
-            <v>1</v>
-          </cell>
-          <cell r="M16">
-            <v>1</v>
-          </cell>
-          <cell r="O16">
-            <v>1</v>
-          </cell>
-          <cell r="Q16">
-            <v>3.2142857142857144</v>
-          </cell>
-          <cell r="R16">
-            <v>64.285714285714292</v>
+            <v>100</v>
+          </cell>
+          <cell r="F16">
+            <v>10</v>
           </cell>
         </row>
         <row r="17">
           <cell r="B17" t="str">
-            <v>Kotavurtla</v>
+            <v>Kothakota</v>
           </cell>
           <cell r="C17">
-            <v>3</v>
+            <v>1</v>
           </cell>
           <cell r="D17">
             <v>1</v>
           </cell>
           <cell r="E17">
-            <v>1</v>
+            <v>100</v>
           </cell>
           <cell r="F17">
-            <v>1</v>
-          </cell>
-          <cell r="G17">
-            <v>1</v>
-          </cell>
-          <cell r="H17">
-            <v>1</v>
-          </cell>
-          <cell r="I17">
-            <v>26</v>
-          </cell>
-          <cell r="J17">
-            <v>1</v>
-          </cell>
-          <cell r="K17">
-            <v>1</v>
-          </cell>
-          <cell r="L17">
-            <v>1</v>
-          </cell>
-          <cell r="M17">
-            <v>1</v>
-          </cell>
-          <cell r="N17">
-            <v>1</v>
-          </cell>
-          <cell r="O17">
-            <v>1</v>
-          </cell>
-          <cell r="P17">
-            <v>1</v>
-          </cell>
-          <cell r="Q17">
-            <v>5</v>
-          </cell>
-          <cell r="R17">
-            <v>100</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="18">
           <cell r="B18" t="str">
-            <v>Kothakota</v>
-          </cell>
-          <cell r="Q18">
-            <v>0</v>
-          </cell>
-          <cell r="R18">
-            <v>0</v>
+            <v>Mahila UPS, Anakapalli</v>
+          </cell>
+          <cell r="E18">
+            <v>100</v>
+          </cell>
+          <cell r="F18">
+            <v>10</v>
           </cell>
         </row>
         <row r="19">
           <cell r="B19" t="str">
-            <v>Mahila UPS, Anakapalli</v>
-          </cell>
-          <cell r="Q19">
-            <v>0</v>
-          </cell>
-          <cell r="R19">
-            <v>0</v>
+            <v>Makavarapalem</v>
+          </cell>
+          <cell r="E19">
+            <v>100</v>
+          </cell>
+          <cell r="F19">
+            <v>10</v>
           </cell>
         </row>
         <row r="20">
           <cell r="B20" t="str">
-            <v>Makavarapalem</v>
-          </cell>
-          <cell r="Q20">
-            <v>0</v>
-          </cell>
-          <cell r="R20">
-            <v>0</v>
+            <v>Munagapaka</v>
+          </cell>
+          <cell r="E20">
+            <v>100</v>
+          </cell>
+          <cell r="F20">
+            <v>10</v>
           </cell>
         </row>
         <row r="21">
           <cell r="B21" t="str">
-            <v>Munagapaka</v>
-          </cell>
-          <cell r="C21">
-            <v>2</v>
-          </cell>
-          <cell r="D21">
-            <v>1</v>
+            <v>Nakkapalli</v>
           </cell>
           <cell r="E21">
-            <v>4</v>
+            <v>100</v>
           </cell>
           <cell r="F21">
-            <v>1</v>
-          </cell>
-          <cell r="G21">
-            <v>6</v>
-          </cell>
-          <cell r="I21">
-            <v>1</v>
-          </cell>
-          <cell r="J21">
-            <v>1</v>
-          </cell>
-          <cell r="K21">
-            <v>3</v>
-          </cell>
-          <cell r="M21">
-            <v>2</v>
-          </cell>
-          <cell r="N21">
-            <v>1</v>
-          </cell>
-          <cell r="Q21">
-            <v>3.5714285714285716</v>
-          </cell>
-          <cell r="R21">
-            <v>71.428571428571431</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="22">
           <cell r="B22" t="str">
-            <v>Nakkapalli</v>
-          </cell>
-          <cell r="Q22">
-            <v>0</v>
-          </cell>
-          <cell r="R22">
-            <v>0</v>
+            <v>Narsipatnam Rural</v>
+          </cell>
+          <cell r="E22">
+            <v>100</v>
+          </cell>
+          <cell r="F22">
+            <v>10</v>
           </cell>
         </row>
         <row r="23">
           <cell r="B23" t="str">
-            <v>Narsipatnam Rural</v>
-          </cell>
-          <cell r="Q23">
-            <v>0</v>
-          </cell>
-          <cell r="R23">
-            <v>0</v>
+            <v>Narsipatnam Town</v>
+          </cell>
+          <cell r="E23">
+            <v>100</v>
+          </cell>
+          <cell r="F23">
+            <v>10</v>
           </cell>
         </row>
         <row r="24">
           <cell r="B24" t="str">
-            <v>Narsipatnam Town</v>
+            <v>Nathavaram</v>
           </cell>
           <cell r="C24">
             <v>1</v>
@@ -16106,239 +16429,98 @@
             <v>1</v>
           </cell>
           <cell r="E24">
-            <v>1</v>
+            <v>100</v>
           </cell>
           <cell r="F24">
-            <v>1</v>
-          </cell>
-          <cell r="G24">
-            <v>1</v>
-          </cell>
-          <cell r="H24">
-            <v>1</v>
-          </cell>
-          <cell r="I24">
-            <v>2</v>
-          </cell>
-          <cell r="J24">
-            <v>1</v>
-          </cell>
-          <cell r="K24">
-            <v>1</v>
-          </cell>
-          <cell r="L24">
-            <v>1</v>
-          </cell>
-          <cell r="M24">
-            <v>1</v>
-          </cell>
-          <cell r="N24">
-            <v>1</v>
-          </cell>
-          <cell r="Q24">
-            <v>4.2857142857142856</v>
-          </cell>
-          <cell r="R24">
-            <v>85.714285714285708</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="25">
           <cell r="B25" t="str">
-            <v>Nathavaram</v>
-          </cell>
-          <cell r="C25">
-            <v>1</v>
-          </cell>
-          <cell r="D25">
-            <v>1</v>
+            <v>Parawada</v>
           </cell>
           <cell r="E25">
-            <v>1</v>
+            <v>100</v>
           </cell>
           <cell r="F25">
-            <v>1</v>
-          </cell>
-          <cell r="H25">
-            <v>1</v>
-          </cell>
-          <cell r="J25">
-            <v>1</v>
-          </cell>
-          <cell r="K25">
-            <v>1</v>
-          </cell>
-          <cell r="L25">
-            <v>1</v>
-          </cell>
-          <cell r="O25">
-            <v>2</v>
-          </cell>
-          <cell r="Q25">
-            <v>3.2142857142857144</v>
-          </cell>
-          <cell r="R25">
-            <v>64.285714285714292</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="26">
           <cell r="B26" t="str">
-            <v>Parawada</v>
-          </cell>
-          <cell r="C26">
-            <v>1</v>
-          </cell>
-          <cell r="D26">
-            <v>1</v>
+            <v>Payakaraopeta</v>
+          </cell>
+          <cell r="E26">
+            <v>100</v>
           </cell>
           <cell r="F26">
-            <v>1</v>
-          </cell>
-          <cell r="G26">
-            <v>1</v>
-          </cell>
-          <cell r="I26">
-            <v>1</v>
-          </cell>
-          <cell r="K26">
-            <v>1</v>
-          </cell>
-          <cell r="L26">
-            <v>1</v>
-          </cell>
-          <cell r="N26">
-            <v>1</v>
-          </cell>
-          <cell r="O26">
-            <v>1</v>
-          </cell>
-          <cell r="Q26">
-            <v>3.2142857142857144</v>
-          </cell>
-          <cell r="R26">
-            <v>64.285714285714292</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="27">
           <cell r="B27" t="str">
-            <v>Payakaraopeta</v>
-          </cell>
-          <cell r="C27">
-            <v>1</v>
-          </cell>
-          <cell r="D27">
-            <v>1</v>
+            <v>Rambilli</v>
           </cell>
           <cell r="E27">
-            <v>1</v>
+            <v>100</v>
           </cell>
           <cell r="F27">
-            <v>1</v>
-          </cell>
-          <cell r="G27">
-            <v>2</v>
-          </cell>
-          <cell r="H27">
-            <v>1</v>
-          </cell>
-          <cell r="I27">
-            <v>1</v>
-          </cell>
-          <cell r="J27">
-            <v>1</v>
-          </cell>
-          <cell r="K27">
-            <v>1</v>
-          </cell>
-          <cell r="L27">
-            <v>1</v>
-          </cell>
-          <cell r="M27">
-            <v>1</v>
-          </cell>
-          <cell r="O27">
-            <v>4</v>
-          </cell>
-          <cell r="Q27">
-            <v>4.2857142857142856</v>
-          </cell>
-          <cell r="R27">
-            <v>85.714285714285708</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="28">
           <cell r="B28" t="str">
-            <v>Rambilli</v>
-          </cell>
-          <cell r="G28">
-            <v>1</v>
-          </cell>
-          <cell r="I28">
-            <v>1</v>
-          </cell>
-          <cell r="Q28">
-            <v>0.7142857142857143</v>
-          </cell>
-          <cell r="R28">
-            <v>14.285714285714285</v>
+            <v>Ravikamatham</v>
+          </cell>
+          <cell r="E28">
+            <v>100</v>
+          </cell>
+          <cell r="F28">
+            <v>10</v>
           </cell>
         </row>
         <row r="29">
           <cell r="B29" t="str">
-            <v>Ravikamatham</v>
-          </cell>
-          <cell r="Q29">
-            <v>0</v>
-          </cell>
-          <cell r="R29">
-            <v>0</v>
+            <v>Rolugunta</v>
+          </cell>
+          <cell r="E29">
+            <v>100</v>
+          </cell>
+          <cell r="F29">
+            <v>10</v>
           </cell>
         </row>
         <row r="30">
           <cell r="B30" t="str">
-            <v>Rolugunta</v>
-          </cell>
-          <cell r="Q30">
-            <v>0</v>
-          </cell>
-          <cell r="R30">
-            <v>0</v>
+            <v>S.Rayavaram</v>
+          </cell>
+          <cell r="C30">
+            <v>1</v>
+          </cell>
+          <cell r="D30">
+            <v>1</v>
+          </cell>
+          <cell r="E30">
+            <v>100</v>
+          </cell>
+          <cell r="F30">
+            <v>10</v>
           </cell>
         </row>
         <row r="31">
           <cell r="B31" t="str">
-            <v>S.Rayavaram</v>
-          </cell>
-          <cell r="C31">
-            <v>1</v>
+            <v>Sabbavaram</v>
+          </cell>
+          <cell r="E31">
+            <v>100</v>
           </cell>
           <cell r="F31">
-            <v>1</v>
-          </cell>
-          <cell r="H31">
-            <v>1</v>
-          </cell>
-          <cell r="J31">
-            <v>1</v>
-          </cell>
-          <cell r="L31">
-            <v>1</v>
-          </cell>
-          <cell r="N31">
-            <v>1</v>
-          </cell>
-          <cell r="O31">
-            <v>1</v>
-          </cell>
-          <cell r="Q31">
-            <v>2.5</v>
-          </cell>
-          <cell r="R31">
-            <v>50</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="32">
           <cell r="B32" t="str">
-            <v>Sabbavaram</v>
+            <v>V.Madugula</v>
           </cell>
           <cell r="C32">
             <v>1</v>
@@ -16347,245 +16529,63 @@
             <v>1</v>
           </cell>
           <cell r="E32">
-            <v>2</v>
+            <v>100</v>
           </cell>
           <cell r="F32">
-            <v>1</v>
-          </cell>
-          <cell r="G32">
-            <v>1</v>
-          </cell>
-          <cell r="H32">
-            <v>1</v>
-          </cell>
-          <cell r="I32">
-            <v>1</v>
-          </cell>
-          <cell r="J32">
-            <v>1</v>
-          </cell>
-          <cell r="K32">
-            <v>1</v>
-          </cell>
-          <cell r="L32">
-            <v>1</v>
-          </cell>
-          <cell r="M32">
-            <v>1</v>
-          </cell>
-          <cell r="N32">
-            <v>1</v>
-          </cell>
-          <cell r="O32">
-            <v>1</v>
-          </cell>
-          <cell r="P32">
-            <v>1</v>
-          </cell>
-          <cell r="Q32">
-            <v>5</v>
-          </cell>
-          <cell r="R32">
-            <v>100</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="33">
           <cell r="B33" t="str">
-            <v>V.Madugula</v>
+            <v>Yelamanchili Rural</v>
+          </cell>
+          <cell r="C33">
+            <v>1</v>
           </cell>
           <cell r="D33">
             <v>1</v>
           </cell>
-          <cell r="I33">
-            <v>1</v>
-          </cell>
-          <cell r="M33">
-            <v>2</v>
-          </cell>
-          <cell r="O33">
-            <v>1</v>
-          </cell>
-          <cell r="Q33">
-            <v>1.4285714285714286</v>
-          </cell>
-          <cell r="R33">
-            <v>28.571428571428569</v>
+          <cell r="E33">
+            <v>100</v>
+          </cell>
+          <cell r="F33">
+            <v>10</v>
           </cell>
         </row>
         <row r="34">
           <cell r="B34" t="str">
-            <v>Yelamanchili Rural</v>
-          </cell>
-          <cell r="C34">
-            <v>1</v>
-          </cell>
-          <cell r="D34">
-            <v>1</v>
+            <v>Yelamanchili Town</v>
           </cell>
           <cell r="E34">
-            <v>1</v>
+            <v>100</v>
           </cell>
           <cell r="F34">
-            <v>1</v>
-          </cell>
-          <cell r="G34">
-            <v>1</v>
-          </cell>
-          <cell r="H34">
-            <v>1</v>
-          </cell>
-          <cell r="J34">
-            <v>1</v>
-          </cell>
-          <cell r="K34">
-            <v>1</v>
-          </cell>
-          <cell r="L34">
-            <v>1</v>
-          </cell>
-          <cell r="N34">
-            <v>1</v>
-          </cell>
-          <cell r="O34">
-            <v>1</v>
-          </cell>
-          <cell r="Q34">
-            <v>3.9285714285714284</v>
-          </cell>
-          <cell r="R34">
-            <v>78.571428571428569</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="35">
           <cell r="B35" t="str">
-            <v>Yelamanchili Town</v>
-          </cell>
-          <cell r="C35">
-            <v>1</v>
-          </cell>
-          <cell r="D35">
-            <v>1</v>
+            <v>Yelamanchili Traffic</v>
           </cell>
           <cell r="E35">
-            <v>2</v>
+            <v>100</v>
           </cell>
           <cell r="F35">
-            <v>1</v>
-          </cell>
-          <cell r="G35">
-            <v>1</v>
-          </cell>
-          <cell r="H35">
-            <v>1</v>
-          </cell>
-          <cell r="I35">
-            <v>1</v>
-          </cell>
-          <cell r="J35">
-            <v>1</v>
-          </cell>
-          <cell r="M35">
-            <v>2</v>
-          </cell>
-          <cell r="O35">
+            <v>10</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="C36">
+            <v>8</v>
+          </cell>
+          <cell r="D36">
             <v>6</v>
           </cell>
-          <cell r="Q35">
-            <v>3.5714285714285716</v>
-          </cell>
-          <cell r="R35">
-            <v>71.428571428571431</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="B36" t="str">
-            <v>Yelamanchili Traffic</v>
-          </cell>
-          <cell r="C36">
-            <v>1</v>
-          </cell>
           <cell r="E36">
-            <v>1</v>
+            <v>96.969696969696969</v>
           </cell>
           <cell r="F36">
-            <v>1</v>
-          </cell>
-          <cell r="G36">
-            <v>1</v>
-          </cell>
-          <cell r="H36">
-            <v>1</v>
-          </cell>
-          <cell r="J36">
-            <v>1</v>
-          </cell>
-          <cell r="K36">
-            <v>1</v>
-          </cell>
-          <cell r="L36">
-            <v>1</v>
-          </cell>
-          <cell r="N36">
-            <v>1</v>
-          </cell>
-          <cell r="O36">
-            <v>1</v>
-          </cell>
-          <cell r="Q36">
-            <v>3.5714285714285716</v>
-          </cell>
-          <cell r="R36">
-            <v>71.428571428571431</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="C37">
-            <v>32</v>
-          </cell>
-          <cell r="D37">
-            <v>14</v>
-          </cell>
-          <cell r="E37">
-            <v>22</v>
-          </cell>
-          <cell r="F37">
-            <v>17</v>
-          </cell>
-          <cell r="G37">
-            <v>25</v>
-          </cell>
-          <cell r="H37">
-            <v>15</v>
-          </cell>
-          <cell r="I37">
-            <v>45</v>
-          </cell>
-          <cell r="J37">
-            <v>17</v>
-          </cell>
-          <cell r="K37">
-            <v>19</v>
-          </cell>
-          <cell r="L37">
-            <v>14</v>
-          </cell>
-          <cell r="M37">
-            <v>26</v>
-          </cell>
-          <cell r="N37">
-            <v>15</v>
-          </cell>
-          <cell r="O37">
-            <v>31</v>
-          </cell>
-          <cell r="P37">
-            <v>3</v>
-          </cell>
-          <cell r="Q37">
-            <v>2.3268398268398265</v>
-          </cell>
-          <cell r="R37">
-            <v>46.53679653679653</v>
+            <v>9.6969696969696972</v>
           </cell>
         </row>
       </sheetData>
@@ -18508,19 +18508,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEAE2537-CADB-4F19-962C-8C0E69D4D2F8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D07933FE-914F-4913-B984-C822D47BE161}">
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:W35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.5703125" customWidth="1"/>
+    <col min="1" max="1" width="23.5546875" customWidth="1"/>
     <col min="2" max="23" width="7" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="84.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" ht="84.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -18591,7 +18591,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="13.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>23</v>
       </c>
@@ -18662,7 +18662,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>24</v>
       </c>
@@ -18731,11 +18731,11 @@
         <v>0</v>
       </c>
       <c r="R3" s="8">
-        <f>VLOOKUP(A3,'[1]17_EDAR'!B:F,4,0)</f>
+        <f>VLOOKUP(A3,'[1]18_EDAR'!B:F,4,0)</f>
         <v>100</v>
       </c>
       <c r="S3" s="8">
-        <f>VLOOKUP(A3,'[1]18_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A3,'[1]17_CCTV_360'!B:S,17,0)</f>
         <v>71.428571428571431</v>
       </c>
       <c r="T3" s="8">
@@ -18755,7 +18755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>25</v>
       </c>
@@ -18824,11 +18824,11 @@
         <v>0</v>
       </c>
       <c r="R4" s="8">
-        <f>VLOOKUP(A4,'[1]17_EDAR'!B:F,4,0)</f>
+        <f>VLOOKUP(A4,'[1]18_EDAR'!B:F,4,0)</f>
         <v>100</v>
       </c>
       <c r="S4" s="8">
-        <f>VLOOKUP(A4,'[1]18_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A4,'[1]17_CCTV_360'!B:S,17,0)</f>
         <v>92.857142857142861</v>
       </c>
       <c r="T4" s="8">
@@ -18848,7 +18848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>26</v>
       </c>
@@ -18917,11 +18917,11 @@
         <v>0</v>
       </c>
       <c r="R5" s="8">
-        <f>VLOOKUP(A5,'[1]17_EDAR'!B:F,4,0)</f>
+        <f>VLOOKUP(A5,'[1]18_EDAR'!B:F,4,0)</f>
         <v>100</v>
       </c>
       <c r="S5" s="8">
-        <f>VLOOKUP(A5,'[1]18_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A5,'[1]17_CCTV_360'!B:S,17,0)</f>
         <v>100</v>
       </c>
       <c r="T5" s="8">
@@ -18941,7 +18941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>27</v>
       </c>
@@ -19010,11 +19010,11 @@
         <v>0</v>
       </c>
       <c r="R6" s="8">
-        <f>VLOOKUP(A6,'[1]17_EDAR'!B:F,4,0)</f>
+        <f>VLOOKUP(A6,'[1]18_EDAR'!B:F,4,0)</f>
         <v>100</v>
       </c>
       <c r="S6" s="8">
-        <f>VLOOKUP(A6,'[1]18_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A6,'[1]17_CCTV_360'!B:S,17,0)</f>
         <v>71.428571428571431</v>
       </c>
       <c r="T6" s="8">
@@ -19034,7 +19034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>28</v>
       </c>
@@ -19103,11 +19103,11 @@
         <v>0</v>
       </c>
       <c r="R7" s="8">
-        <f>VLOOKUP(A7,'[1]17_EDAR'!B:F,4,0)</f>
+        <f>VLOOKUP(A7,'[1]18_EDAR'!B:F,4,0)</f>
         <v>100</v>
       </c>
       <c r="S7" s="8">
-        <f>VLOOKUP(A7,'[1]18_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A7,'[1]17_CCTV_360'!B:S,17,0)</f>
         <v>28.571428571428569</v>
       </c>
       <c r="T7" s="8">
@@ -19127,7 +19127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>29</v>
       </c>
@@ -19196,11 +19196,11 @@
         <v>0</v>
       </c>
       <c r="R8" s="8">
-        <f>VLOOKUP(A8,'[1]17_EDAR'!B:F,4,0)</f>
+        <f>VLOOKUP(A8,'[1]18_EDAR'!B:F,4,0)</f>
         <v>100</v>
       </c>
       <c r="S8" s="8">
-        <f>VLOOKUP(A8,'[1]18_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A8,'[1]17_CCTV_360'!B:S,17,0)</f>
         <v>35.714285714285715</v>
       </c>
       <c r="T8" s="8">
@@ -19220,7 +19220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>30</v>
       </c>
@@ -19289,11 +19289,11 @@
         <v>0</v>
       </c>
       <c r="R9" s="8">
-        <f>VLOOKUP(A9,'[1]17_EDAR'!B:F,4,0)</f>
+        <f>VLOOKUP(A9,'[1]18_EDAR'!B:F,4,0)</f>
         <v>100</v>
       </c>
       <c r="S9" s="8">
-        <f>VLOOKUP(A9,'[1]18_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A9,'[1]17_CCTV_360'!B:S,17,0)</f>
         <v>7.1428571428571423</v>
       </c>
       <c r="T9" s="8">
@@ -19313,7 +19313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>31</v>
       </c>
@@ -19382,11 +19382,11 @@
         <v>0</v>
       </c>
       <c r="R10" s="8">
-        <f>VLOOKUP(A10,'[1]17_EDAR'!B:F,4,0)</f>
+        <f>VLOOKUP(A10,'[1]18_EDAR'!B:F,4,0)</f>
         <v>100</v>
       </c>
       <c r="S10" s="8">
-        <f>VLOOKUP(A10,'[1]18_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A10,'[1]17_CCTV_360'!B:S,17,0)</f>
         <v>71.428571428571431</v>
       </c>
       <c r="T10" s="8">
@@ -19406,7 +19406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>32</v>
       </c>
@@ -19475,11 +19475,11 @@
         <v>0</v>
       </c>
       <c r="R11" s="8">
-        <f>VLOOKUP(A11,'[1]17_EDAR'!B:F,4,0)</f>
+        <f>VLOOKUP(A11,'[1]18_EDAR'!B:F,4,0)</f>
         <v>100</v>
       </c>
       <c r="S11" s="8">
-        <f>VLOOKUP(A11,'[1]18_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A11,'[1]17_CCTV_360'!B:S,17,0)</f>
         <v>14.285714285714285</v>
       </c>
       <c r="T11" s="8">
@@ -19499,7 +19499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>33</v>
       </c>
@@ -19568,11 +19568,11 @@
         <v>0</v>
       </c>
       <c r="R12" s="8">
-        <f>VLOOKUP(A12,'[1]17_EDAR'!B:F,4,0)</f>
+        <f>VLOOKUP(A12,'[1]18_EDAR'!B:F,4,0)</f>
         <v>100</v>
       </c>
       <c r="S12" s="8">
-        <f>VLOOKUP(A12,'[1]18_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A12,'[1]17_CCTV_360'!B:S,17,0)</f>
         <v>78.571428571428569</v>
       </c>
       <c r="T12" s="8">
@@ -19592,7 +19592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>34</v>
       </c>
@@ -19661,11 +19661,11 @@
         <v>0</v>
       </c>
       <c r="R13" s="8">
-        <f>VLOOKUP(A13,'[1]17_EDAR'!B:F,4,0)</f>
+        <f>VLOOKUP(A13,'[1]18_EDAR'!B:F,4,0)</f>
         <v>100</v>
       </c>
       <c r="S13" s="8">
-        <f>VLOOKUP(A13,'[1]18_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A13,'[1]17_CCTV_360'!B:S,17,0)</f>
         <v>7.1428571428571423</v>
       </c>
       <c r="T13" s="8">
@@ -19685,7 +19685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>35</v>
       </c>
@@ -19754,11 +19754,11 @@
         <v>0</v>
       </c>
       <c r="R14" s="8">
-        <f>VLOOKUP(A14,'[1]17_EDAR'!B:F,4,0)</f>
+        <f>VLOOKUP(A14,'[1]18_EDAR'!B:F,4,0)</f>
         <v>100</v>
       </c>
       <c r="S14" s="8">
-        <f>VLOOKUP(A14,'[1]18_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A14,'[1]17_CCTV_360'!B:S,17,0)</f>
         <v>7.1428571428571423</v>
       </c>
       <c r="T14" s="8">
@@ -19778,7 +19778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>36</v>
       </c>
@@ -19847,11 +19847,11 @@
         <v>0</v>
       </c>
       <c r="R15" s="8">
-        <f>VLOOKUP(A15,'[1]17_EDAR'!B:F,4,0)</f>
+        <f>VLOOKUP(A15,'[1]18_EDAR'!B:F,4,0)</f>
         <v>0</v>
       </c>
       <c r="S15" s="8">
-        <f>VLOOKUP(A15,'[1]18_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A15,'[1]17_CCTV_360'!B:S,17,0)</f>
         <v>64.285714285714292</v>
       </c>
       <c r="T15" s="8">
@@ -19871,7 +19871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>37</v>
       </c>
@@ -19940,11 +19940,11 @@
         <v>0</v>
       </c>
       <c r="R16" s="8">
-        <f>VLOOKUP(A16,'[1]17_EDAR'!B:F,4,0)</f>
+        <f>VLOOKUP(A16,'[1]18_EDAR'!B:F,4,0)</f>
         <v>100</v>
       </c>
       <c r="S16" s="8">
-        <f>VLOOKUP(A16,'[1]18_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A16,'[1]17_CCTV_360'!B:S,17,0)</f>
         <v>100</v>
       </c>
       <c r="T16" s="8">
@@ -19964,7 +19964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>38</v>
       </c>
@@ -20033,11 +20033,11 @@
         <v>0</v>
       </c>
       <c r="R17" s="8">
-        <f>VLOOKUP(A17,'[1]17_EDAR'!B:F,4,0)</f>
+        <f>VLOOKUP(A17,'[1]18_EDAR'!B:F,4,0)</f>
         <v>100</v>
       </c>
       <c r="S17" s="8">
-        <f>VLOOKUP(A17,'[1]18_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A17,'[1]17_CCTV_360'!B:S,17,0)</f>
         <v>0</v>
       </c>
       <c r="T17" s="8">
@@ -20057,7 +20057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>39</v>
       </c>
@@ -20126,11 +20126,11 @@
         <v>0</v>
       </c>
       <c r="R18" s="8">
-        <f>VLOOKUP(A18,'[1]17_EDAR'!B:F,4,0)</f>
+        <f>VLOOKUP(A18,'[1]18_EDAR'!B:F,4,0)</f>
         <v>100</v>
       </c>
       <c r="S18" s="8">
-        <f>VLOOKUP(A18,'[1]18_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A18,'[1]17_CCTV_360'!B:S,17,0)</f>
         <v>0</v>
       </c>
       <c r="T18" s="8">
@@ -20150,7 +20150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>40</v>
       </c>
@@ -20219,11 +20219,11 @@
         <v>0</v>
       </c>
       <c r="R19" s="8">
-        <f>VLOOKUP(A19,'[1]17_EDAR'!B:F,4,0)</f>
+        <f>VLOOKUP(A19,'[1]18_EDAR'!B:F,4,0)</f>
         <v>100</v>
       </c>
       <c r="S19" s="8">
-        <f>VLOOKUP(A19,'[1]18_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A19,'[1]17_CCTV_360'!B:S,17,0)</f>
         <v>0</v>
       </c>
       <c r="T19" s="8">
@@ -20243,7 +20243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>41</v>
       </c>
@@ -20312,11 +20312,11 @@
         <v>0</v>
       </c>
       <c r="R20" s="8">
-        <f>VLOOKUP(A20,'[1]17_EDAR'!B:F,4,0)</f>
+        <f>VLOOKUP(A20,'[1]18_EDAR'!B:F,4,0)</f>
         <v>100</v>
       </c>
       <c r="S20" s="8">
-        <f>VLOOKUP(A20,'[1]18_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A20,'[1]17_CCTV_360'!B:S,17,0)</f>
         <v>71.428571428571431</v>
       </c>
       <c r="T20" s="8">
@@ -20336,7 +20336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>42</v>
       </c>
@@ -20405,11 +20405,11 @@
         <v>0</v>
       </c>
       <c r="R21" s="8">
-        <f>VLOOKUP(A21,'[1]17_EDAR'!B:F,4,0)</f>
+        <f>VLOOKUP(A21,'[1]18_EDAR'!B:F,4,0)</f>
         <v>100</v>
       </c>
       <c r="S21" s="8">
-        <f>VLOOKUP(A21,'[1]18_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A21,'[1]17_CCTV_360'!B:S,17,0)</f>
         <v>0</v>
       </c>
       <c r="T21" s="8">
@@ -20429,7 +20429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>43</v>
       </c>
@@ -20498,11 +20498,11 @@
         <v>0</v>
       </c>
       <c r="R22" s="8">
-        <f>VLOOKUP(A22,'[1]17_EDAR'!B:F,4,0)</f>
+        <f>VLOOKUP(A22,'[1]18_EDAR'!B:F,4,0)</f>
         <v>100</v>
       </c>
       <c r="S22" s="8">
-        <f>VLOOKUP(A22,'[1]18_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A22,'[1]17_CCTV_360'!B:S,17,0)</f>
         <v>0</v>
       </c>
       <c r="T22" s="8">
@@ -20522,7 +20522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>44</v>
       </c>
@@ -20591,11 +20591,11 @@
         <v>0</v>
       </c>
       <c r="R23" s="8">
-        <f>VLOOKUP(A23,'[1]17_EDAR'!B:F,4,0)</f>
+        <f>VLOOKUP(A23,'[1]18_EDAR'!B:F,4,0)</f>
         <v>100</v>
       </c>
       <c r="S23" s="8">
-        <f>VLOOKUP(A23,'[1]18_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A23,'[1]17_CCTV_360'!B:S,17,0)</f>
         <v>85.714285714285708</v>
       </c>
       <c r="T23" s="8">
@@ -20615,7 +20615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>45</v>
       </c>
@@ -20684,11 +20684,11 @@
         <v>0</v>
       </c>
       <c r="R24" s="8">
-        <f>VLOOKUP(A24,'[1]17_EDAR'!B:F,4,0)</f>
+        <f>VLOOKUP(A24,'[1]18_EDAR'!B:F,4,0)</f>
         <v>100</v>
       </c>
       <c r="S24" s="8">
-        <f>VLOOKUP(A24,'[1]18_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A24,'[1]17_CCTV_360'!B:S,17,0)</f>
         <v>64.285714285714292</v>
       </c>
       <c r="T24" s="8">
@@ -20708,7 +20708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>46</v>
       </c>
@@ -20777,11 +20777,11 @@
         <v>0</v>
       </c>
       <c r="R25" s="8">
-        <f>VLOOKUP(A25,'[1]17_EDAR'!B:F,4,0)</f>
+        <f>VLOOKUP(A25,'[1]18_EDAR'!B:F,4,0)</f>
         <v>100</v>
       </c>
       <c r="S25" s="8">
-        <f>VLOOKUP(A25,'[1]18_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A25,'[1]17_CCTV_360'!B:S,17,0)</f>
         <v>64.285714285714292</v>
       </c>
       <c r="T25" s="8">
@@ -20801,7 +20801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>47</v>
       </c>
@@ -20870,11 +20870,11 @@
         <v>0</v>
       </c>
       <c r="R26" s="8">
-        <f>VLOOKUP(A26,'[1]17_EDAR'!B:F,4,0)</f>
+        <f>VLOOKUP(A26,'[1]18_EDAR'!B:F,4,0)</f>
         <v>100</v>
       </c>
       <c r="S26" s="8">
-        <f>VLOOKUP(A26,'[1]18_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A26,'[1]17_CCTV_360'!B:S,17,0)</f>
         <v>85.714285714285708</v>
       </c>
       <c r="T26" s="8">
@@ -20894,7 +20894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>48</v>
       </c>
@@ -20963,11 +20963,11 @@
         <v>0</v>
       </c>
       <c r="R27" s="8">
-        <f>VLOOKUP(A27,'[1]17_EDAR'!B:F,4,0)</f>
+        <f>VLOOKUP(A27,'[1]18_EDAR'!B:F,4,0)</f>
         <v>100</v>
       </c>
       <c r="S27" s="8">
-        <f>VLOOKUP(A27,'[1]18_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A27,'[1]17_CCTV_360'!B:S,17,0)</f>
         <v>14.285714285714285</v>
       </c>
       <c r="T27" s="8">
@@ -20987,7 +20987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>49</v>
       </c>
@@ -21056,11 +21056,11 @@
         <v>0</v>
       </c>
       <c r="R28" s="8">
-        <f>VLOOKUP(A28,'[1]17_EDAR'!B:F,4,0)</f>
+        <f>VLOOKUP(A28,'[1]18_EDAR'!B:F,4,0)</f>
         <v>100</v>
       </c>
       <c r="S28" s="8">
-        <f>VLOOKUP(A28,'[1]18_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A28,'[1]17_CCTV_360'!B:S,17,0)</f>
         <v>0</v>
       </c>
       <c r="T28" s="8">
@@ -21080,7 +21080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>50</v>
       </c>
@@ -21149,11 +21149,11 @@
         <v>0</v>
       </c>
       <c r="R29" s="8">
-        <f>VLOOKUP(A29,'[1]17_EDAR'!B:F,4,0)</f>
+        <f>VLOOKUP(A29,'[1]18_EDAR'!B:F,4,0)</f>
         <v>100</v>
       </c>
       <c r="S29" s="8">
-        <f>VLOOKUP(A29,'[1]18_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A29,'[1]17_CCTV_360'!B:S,17,0)</f>
         <v>0</v>
       </c>
       <c r="T29" s="8">
@@ -21173,7 +21173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>51</v>
       </c>
@@ -21242,11 +21242,11 @@
         <v>0</v>
       </c>
       <c r="R30" s="8">
-        <f>VLOOKUP(A30,'[1]17_EDAR'!B:F,4,0)</f>
+        <f>VLOOKUP(A30,'[1]18_EDAR'!B:F,4,0)</f>
         <v>100</v>
       </c>
       <c r="S30" s="8">
-        <f>VLOOKUP(A30,'[1]18_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A30,'[1]17_CCTV_360'!B:S,17,0)</f>
         <v>50</v>
       </c>
       <c r="T30" s="8">
@@ -21266,7 +21266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>52</v>
       </c>
@@ -21335,11 +21335,11 @@
         <v>0</v>
       </c>
       <c r="R31" s="8">
-        <f>VLOOKUP(A31,'[1]17_EDAR'!B:F,4,0)</f>
+        <f>VLOOKUP(A31,'[1]18_EDAR'!B:F,4,0)</f>
         <v>100</v>
       </c>
       <c r="S31" s="8">
-        <f>VLOOKUP(A31,'[1]18_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A31,'[1]17_CCTV_360'!B:S,17,0)</f>
         <v>100</v>
       </c>
       <c r="T31" s="8">
@@ -21359,7 +21359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>53</v>
       </c>
@@ -21428,11 +21428,11 @@
         <v>0</v>
       </c>
       <c r="R32" s="8">
-        <f>VLOOKUP(A32,'[1]17_EDAR'!B:F,4,0)</f>
+        <f>VLOOKUP(A32,'[1]18_EDAR'!B:F,4,0)</f>
         <v>100</v>
       </c>
       <c r="S32" s="8">
-        <f>VLOOKUP(A32,'[1]18_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A32,'[1]17_CCTV_360'!B:S,17,0)</f>
         <v>28.571428571428569</v>
       </c>
       <c r="T32" s="8">
@@ -21452,7 +21452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>54</v>
       </c>
@@ -21521,11 +21521,11 @@
         <v>0</v>
       </c>
       <c r="R33" s="8">
-        <f>VLOOKUP(A33,'[1]17_EDAR'!B:F,4,0)</f>
+        <f>VLOOKUP(A33,'[1]18_EDAR'!B:F,4,0)</f>
         <v>100</v>
       </c>
       <c r="S33" s="8">
-        <f>VLOOKUP(A33,'[1]18_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A33,'[1]17_CCTV_360'!B:S,17,0)</f>
         <v>78.571428571428569</v>
       </c>
       <c r="T33" s="8">
@@ -21545,7 +21545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
         <v>55</v>
       </c>
@@ -21614,11 +21614,11 @@
         <v>0</v>
       </c>
       <c r="R34" s="8">
-        <f>VLOOKUP(A34,'[1]17_EDAR'!B:F,4,0)</f>
+        <f>VLOOKUP(A34,'[1]18_EDAR'!B:F,4,0)</f>
         <v>100</v>
       </c>
       <c r="S34" s="8">
-        <f>VLOOKUP(A34,'[1]18_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A34,'[1]17_CCTV_360'!B:S,17,0)</f>
         <v>71.428571428571431</v>
       </c>
       <c r="T34" s="8">
@@ -21638,7 +21638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:23" s="9" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
         <v>56</v>
       </c>
@@ -21707,11 +21707,11 @@
         <v>0</v>
       </c>
       <c r="R35" s="8">
-        <f>VLOOKUP(A35,'[1]17_EDAR'!B:F,4,0)</f>
+        <f>VLOOKUP(A35,'[1]18_EDAR'!B:F,4,0)</f>
         <v>100</v>
       </c>
       <c r="S35" s="8">
-        <f>VLOOKUP(A35,'[1]18_CCTV_360'!B:S,17,0)</f>
+        <f>VLOOKUP(A35,'[1]17_CCTV_360'!B:S,17,0)</f>
         <v>71.428571428571431</v>
       </c>
       <c r="T35" s="8">
